--- a/backend/app/platforms/logimat/template.xlsx
+++ b/backend/app/platforms/logimat/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diana.ramirez\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\zymo-intranet\backend\app\platforms\logimat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A80D17D-80E3-4C71-9A2A-961729F8CA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E492E1C1-5C35-4AE6-88F0-A2B36162E5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{24C06BA4-7066-42F3-8310-534950C36D3C}"/>
+    <workbookView xWindow="-19310" yWindow="-620" windowWidth="19420" windowHeight="11500" xr2:uid="{24C06BA4-7066-42F3-8310-534950C36D3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="53">
   <si>
     <t xml:space="preserve">         LOGIMAT S.A.S.</t>
   </si>
@@ -241,14 +241,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,12 +325,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -456,7 +450,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="50">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -471,21 +465,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -607,19 +586,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1046,30 +1012,33 @@
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1080,377 +1049,356 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="4" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="2" borderId="19" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="2" borderId="20" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="2" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="27" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="21" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="22" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="23" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="24" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="25" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="26" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="27" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="28" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="29" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="17" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="18" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="33" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="3" borderId="17" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="3" borderId="18" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="3" borderId="33" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="11" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="12" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="13" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="32" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="31" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="14" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="16" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="21" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="22" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="23" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="24" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="25" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="26" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="3" borderId="19" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="3" borderId="20" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="3" borderId="35" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="13" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="14" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="34" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="33" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="16" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="17" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="18" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="19" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="20" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="35" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1484,7 +1432,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="0" cy="330989"/>
@@ -1912,21 +1860,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A804AB5-9B7D-4CE4-BE89-EA920ADDC374}">
-  <dimension ref="A1:IV66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:IV68"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="3.26953125" style="2" customWidth="1"/>
-    <col min="3" max="4" width="14.54296875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.90625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="47.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21.54296875" style="2" customWidth="1"/>
-    <col min="9" max="10" width="3.26953125" style="2" customWidth="1"/>
-    <col min="11" max="256" width="0" style="2" hidden="1"/>
-    <col min="257" max="16384" width="10.453125" style="2" hidden="1"/>
+    <col min="1" max="2" width="3.28515625" style="2" customWidth="1"/>
+    <col min="3" max="4" width="14.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="47.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" style="2" customWidth="1"/>
+    <col min="9" max="10" width="3.28515625" style="2" customWidth="1"/>
+    <col min="11" max="256" width="0" style="2" hidden="1" customWidth="1"/>
+    <col min="257" max="16384" width="10.42578125" style="2" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1938,101 +1886,101 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="C3" s="118" t="e" vm="1">
+      <c r="C3" s="117" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="D3" s="119"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="115" t="s">
+      <c r="D3" s="118"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="116"/>
-      <c r="H3" s="117"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="125"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="123"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="122"/>
       <c r="F4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="113" t="s">
+      <c r="G4" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="114"/>
+      <c r="H4" s="127"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="C5" s="110" t="s">
+      <c r="C5" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="111"/>
-      <c r="E5" s="112"/>
-      <c r="F5" s="104">
+      <c r="D5" s="129"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="102">
         <v>46126</v>
       </c>
-      <c r="G5" s="105"/>
-      <c r="H5" s="106"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="104"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="C6" s="107" t="s">
+      <c r="C6" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="104" t="s">
+      <c r="D6" s="100"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="105"/>
-      <c r="H6" s="106"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="104"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="C7" s="107" t="s">
+      <c r="C7" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="108"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="104" t="s">
+      <c r="D7" s="100"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="105"/>
-      <c r="H7" s="106"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="104"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="C8" s="130" t="s">
+      <c r="C8" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="131"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="127" t="s">
+      <c r="D8" s="106"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="128"/>
-      <c r="H8" s="129"/>
+      <c r="G8" s="109"/>
+      <c r="H8" s="110"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="C9" s="124" t="s">
+      <c r="C9" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="125"/>
-      <c r="E9" s="126"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="113"/>
       <c r="F9" s="4" t="s">
         <v>11</v>
       </c>
@@ -2044,7 +1992,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="C10" s="7" t="s">
         <v>14</v>
@@ -2063,7 +2011,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="11"/>
     </row>
-    <row r="11" spans="1:11" ht="32" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="C11" s="12">
         <v>1</v>
@@ -2085,1361 +2033,947 @@
       <c r="J11" s="1"/>
       <c r="K11" s="11"/>
     </row>
-    <row r="12" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="C12" s="12">
-        <v>5</v>
-      </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H12" s="21">
-        <f t="shared" ref="H12:H30" si="0">+G12*D12</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D12" s="13">
+        <v>1</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="15">
+        <v>360001</v>
+      </c>
+      <c r="H12" s="16">
+        <f t="shared" ref="H12:H32" si="0">+G12*D12</f>
+        <v>360001</v>
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="C13" s="12">
-        <v>5</v>
-      </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H13" s="21">
+        <v>1</v>
+      </c>
+      <c r="D13" s="13">
+        <v>1</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="15">
+        <v>360002</v>
+      </c>
+      <c r="H13" s="16">
+        <f t="shared" si="0"/>
+        <v>360002</v>
+      </c>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="C14" s="12">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13">
+        <v>1</v>
+      </c>
+      <c r="E14" s="12"/>
+      <c r="F14" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="15">
+        <v>360003</v>
+      </c>
+      <c r="H14" s="16">
+        <f t="shared" si="0"/>
+        <v>360003</v>
+      </c>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="C15" s="12">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13">
+        <v>1</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="15">
+        <v>360004</v>
+      </c>
+      <c r="H15" s="16">
+        <f t="shared" si="0"/>
+        <v>360004</v>
+      </c>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="C16" s="12">
+        <v>1</v>
+      </c>
+      <c r="D16" s="13">
+        <v>1</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="15">
+        <v>360005</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>360005</v>
+      </c>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="C17" s="12">
+        <v>1</v>
+      </c>
+      <c r="D17" s="13">
+        <v>1</v>
+      </c>
+      <c r="E17" s="12"/>
+      <c r="F17" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="15">
+        <v>360006</v>
+      </c>
+      <c r="H17" s="16">
+        <f t="shared" si="0"/>
+        <v>360006</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="C18" s="12">
+        <v>1</v>
+      </c>
+      <c r="D18" s="13">
+        <v>1</v>
+      </c>
+      <c r="E18" s="12"/>
+      <c r="F18" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="15">
+        <v>360007</v>
+      </c>
+      <c r="H18" s="16">
+        <f t="shared" si="0"/>
+        <v>360007</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="C19" s="12">
+        <v>1</v>
+      </c>
+      <c r="D19" s="13">
+        <v>1</v>
+      </c>
+      <c r="E19" s="12"/>
+      <c r="F19" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="15">
+        <v>360008</v>
+      </c>
+      <c r="H19" s="16">
+        <f t="shared" si="0"/>
+        <v>360008</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="C20" s="12">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13">
+        <v>1</v>
+      </c>
+      <c r="E20" s="12"/>
+      <c r="F20" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="15">
+        <v>360009</v>
+      </c>
+      <c r="H20" s="16">
+        <f t="shared" si="0"/>
+        <v>360009</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="C21" s="12">
+        <v>1</v>
+      </c>
+      <c r="D21" s="13">
+        <v>1</v>
+      </c>
+      <c r="E21" s="12"/>
+      <c r="F21" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="15">
+        <v>360010</v>
+      </c>
+      <c r="H21" s="16">
+        <f t="shared" si="0"/>
+        <v>360010</v>
+      </c>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="C22" s="12">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13">
+        <v>1</v>
+      </c>
+      <c r="E22" s="12"/>
+      <c r="F22" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="15">
+        <v>360011</v>
+      </c>
+      <c r="H22" s="16">
+        <f t="shared" si="0"/>
+        <v>360011</v>
+      </c>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="C23" s="12">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13">
+        <v>1</v>
+      </c>
+      <c r="E23" s="12"/>
+      <c r="F23" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="15">
+        <v>360012</v>
+      </c>
+      <c r="H23" s="16">
+        <f t="shared" si="0"/>
+        <v>360012</v>
+      </c>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="C24" s="12">
+        <v>1</v>
+      </c>
+      <c r="D24" s="13">
+        <v>1</v>
+      </c>
+      <c r="E24" s="12"/>
+      <c r="F24" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="15">
+        <v>360013</v>
+      </c>
+      <c r="H24" s="16">
+        <f t="shared" si="0"/>
+        <v>360013</v>
+      </c>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="C25" s="12">
+        <v>1</v>
+      </c>
+      <c r="D25" s="13">
+        <v>1</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="15">
+        <v>360014</v>
+      </c>
+      <c r="H25" s="16">
+        <f t="shared" si="0"/>
+        <v>360014</v>
+      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="C26" s="12">
+        <v>1</v>
+      </c>
+      <c r="D26" s="13">
+        <v>1</v>
+      </c>
+      <c r="E26" s="12"/>
+      <c r="F26" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="15">
+        <v>360015</v>
+      </c>
+      <c r="H26" s="16">
+        <f t="shared" si="0"/>
+        <v>360015</v>
+      </c>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="C27" s="12">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13">
+        <v>1</v>
+      </c>
+      <c r="E27" s="12"/>
+      <c r="F27" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="15">
+        <v>360016</v>
+      </c>
+      <c r="H27" s="16">
+        <f t="shared" si="0"/>
+        <v>360016</v>
+      </c>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="C28" s="12">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13">
+        <v>1</v>
+      </c>
+      <c r="E28" s="12"/>
+      <c r="F28" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="15">
+        <v>360017</v>
+      </c>
+      <c r="H28" s="16">
+        <f t="shared" si="0"/>
+        <v>360017</v>
+      </c>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="C29" s="12">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13">
+        <v>1</v>
+      </c>
+      <c r="E29" s="12"/>
+      <c r="F29" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="15">
+        <v>360018</v>
+      </c>
+      <c r="H29" s="16">
+        <f t="shared" si="0"/>
+        <v>360018</v>
+      </c>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="C30" s="12">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13">
+        <v>1</v>
+      </c>
+      <c r="E30" s="12"/>
+      <c r="F30" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="15">
+        <v>360019</v>
+      </c>
+      <c r="H30" s="16">
+        <f t="shared" si="0"/>
+        <v>360019</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="C14" s="12">
-        <v>5</v>
-      </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H14" s="21">
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1"/>
-      <c r="C15" s="12">
-        <v>5</v>
-      </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H15" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1"/>
-      <c r="C16" s="12">
-        <v>5</v>
-      </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H16" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1"/>
-      <c r="C17" s="12">
-        <v>5</v>
-      </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H17" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1"/>
-      <c r="C18" s="12">
-        <v>5</v>
-      </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H18" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1"/>
-      <c r="C19" s="12">
-        <v>5</v>
-      </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H19" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1"/>
-      <c r="C20" s="12">
-        <v>5</v>
-      </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H20" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1"/>
-      <c r="C21" s="12">
-        <v>5</v>
-      </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H21" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="1"/>
-      <c r="C22" s="12">
-        <v>5</v>
-      </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H22" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="1"/>
-      <c r="C23" s="12">
-        <v>5</v>
-      </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H23" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="1"/>
-      <c r="C24" s="12">
-        <v>5</v>
-      </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H24" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1"/>
-      <c r="C25" s="12">
-        <v>5</v>
-      </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H25" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="1"/>
-      <c r="C26" s="12">
-        <v>5</v>
-      </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H26" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1"/>
-      <c r="C27" s="12">
-        <v>5</v>
-      </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H27" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="1"/>
-      <c r="C28" s="12">
-        <v>5</v>
-      </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H28" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1"/>
-      <c r="C29" s="12">
-        <v>5</v>
-      </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H29" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="1"/>
-      <c r="C30" s="12">
-        <v>5</v>
-      </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="20">
-        <v>160000</v>
-      </c>
-      <c r="H30" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="1"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="25"/>
-      <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="1"/>
-      <c r="C32" s="26" t="s">
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="C33" s="114"/>
+      <c r="D33" s="115"/>
+      <c r="E33" s="115"/>
+      <c r="F33" s="115"/>
+      <c r="G33" s="115"/>
+      <c r="H33" s="116"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:256" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+      <c r="C34" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="28"/>
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:256" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="29"/>
-      <c r="C33" s="30" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="89"/>
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="C35" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="32" t="s">
+      <c r="D35" s="92"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G33" s="33"/>
-      <c r="H33" s="34"/>
-      <c r="J33" s="29"/>
-    </row>
-    <row r="34" spans="1:256" ht="16" x14ac:dyDescent="0.35">
-      <c r="A34" s="29"/>
-      <c r="C34" s="35" t="s">
+      <c r="G35" s="19"/>
+      <c r="H35" s="20"/>
+      <c r="J35" s="17"/>
+    </row>
+    <row r="36" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="C36" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="38">
+      <c r="D36" s="94"/>
+      <c r="E36" s="94"/>
+      <c r="F36" s="94"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="21">
         <f>SUM(H11:H11)</f>
         <v>360000</v>
       </c>
-      <c r="J34" s="29"/>
-    </row>
-    <row r="35" spans="1:256" ht="16" x14ac:dyDescent="0.35">
-      <c r="A35" s="29"/>
-      <c r="C35" s="35" t="s">
+      <c r="J36" s="17"/>
+    </row>
+    <row r="37" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="C37" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="38">
-        <f>+H34*19%</f>
+      <c r="D37" s="94"/>
+      <c r="E37" s="94"/>
+      <c r="F37" s="94"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="21">
+        <f>+H36*19%</f>
         <v>68400</v>
       </c>
-      <c r="J35" s="29"/>
-    </row>
-    <row r="36" spans="1:256" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="39"/>
-      <c r="C36" s="40" t="s">
+      <c r="J37" s="17"/>
+    </row>
+    <row r="38" spans="1:256" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="22"/>
+      <c r="C38" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="43">
-        <f>+H34+H35</f>
+      <c r="D38" s="97"/>
+      <c r="E38" s="97"/>
+      <c r="F38" s="97"/>
+      <c r="G38" s="98"/>
+      <c r="H38" s="23">
+        <f>+H36+H37</f>
         <v>428400</v>
       </c>
-      <c r="I36" s="2"/>
-      <c r="J36" s="39"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="2"/>
-      <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
-      <c r="V36" s="2"/>
-      <c r="W36" s="2"/>
-      <c r="X36" s="2"/>
-      <c r="Y36" s="2"/>
-      <c r="Z36" s="2"/>
-      <c r="AA36" s="2"/>
-      <c r="AB36" s="2"/>
-      <c r="AC36" s="2"/>
-      <c r="AD36" s="2"/>
-      <c r="AE36" s="2"/>
-      <c r="AF36" s="2"/>
-      <c r="AG36" s="2"/>
-      <c r="AH36" s="2"/>
-      <c r="AI36" s="2"/>
-      <c r="AJ36" s="2"/>
-      <c r="AK36" s="2"/>
-      <c r="AL36" s="2"/>
-      <c r="AM36" s="2"/>
-      <c r="AN36" s="2"/>
-      <c r="AO36" s="2"/>
-      <c r="AP36" s="2"/>
-      <c r="AQ36" s="2"/>
-      <c r="AR36" s="2"/>
-      <c r="AS36" s="2"/>
-      <c r="AT36" s="2"/>
-      <c r="AU36" s="2"/>
-      <c r="AV36" s="2"/>
-      <c r="AW36" s="2"/>
-      <c r="AX36" s="2"/>
-      <c r="AY36" s="2"/>
-      <c r="AZ36" s="2"/>
-      <c r="BA36" s="2"/>
-      <c r="BB36" s="2"/>
-      <c r="BC36" s="2"/>
-      <c r="BD36" s="2"/>
-      <c r="BE36" s="2"/>
-      <c r="BF36" s="2"/>
-      <c r="BG36" s="2"/>
-      <c r="BH36" s="2"/>
-      <c r="BI36" s="2"/>
-      <c r="BJ36" s="2"/>
-      <c r="BK36" s="2"/>
-      <c r="BL36" s="2"/>
-      <c r="BM36" s="2"/>
-      <c r="BN36" s="2"/>
-      <c r="BO36" s="2"/>
-      <c r="BP36" s="2"/>
-      <c r="BQ36" s="2"/>
-      <c r="BR36" s="2"/>
-      <c r="BS36" s="2"/>
-      <c r="BT36" s="2"/>
-      <c r="BU36" s="2"/>
-      <c r="BV36" s="2"/>
-      <c r="BW36" s="2"/>
-      <c r="BX36" s="2"/>
-      <c r="BY36" s="2"/>
-      <c r="BZ36" s="2"/>
-      <c r="CA36" s="2"/>
-      <c r="CB36" s="2"/>
-      <c r="CC36" s="2"/>
-      <c r="CD36" s="2"/>
-      <c r="CE36" s="2"/>
-      <c r="CF36" s="2"/>
-      <c r="CG36" s="2"/>
-      <c r="CH36" s="2"/>
-      <c r="CI36" s="2"/>
-      <c r="CJ36" s="2"/>
-      <c r="CK36" s="2"/>
-      <c r="CL36" s="2"/>
-      <c r="CM36" s="2"/>
-      <c r="CN36" s="2"/>
-      <c r="CO36" s="2"/>
-      <c r="CP36" s="2"/>
-      <c r="CQ36" s="2"/>
-      <c r="CR36" s="2"/>
-      <c r="CS36" s="2"/>
-      <c r="CT36" s="2"/>
-      <c r="CU36" s="2"/>
-      <c r="CV36" s="2"/>
-      <c r="CW36" s="2"/>
-      <c r="CX36" s="2"/>
-      <c r="CY36" s="2"/>
-      <c r="CZ36" s="2"/>
-      <c r="DA36" s="2"/>
-      <c r="DB36" s="2"/>
-      <c r="DC36" s="2"/>
-      <c r="DD36" s="2"/>
-      <c r="DE36" s="2"/>
-      <c r="DF36" s="2"/>
-      <c r="DG36" s="2"/>
-      <c r="DH36" s="2"/>
-      <c r="DI36" s="2"/>
-      <c r="DJ36" s="2"/>
-      <c r="DK36" s="2"/>
-      <c r="DL36" s="2"/>
-      <c r="DM36" s="2"/>
-      <c r="DN36" s="2"/>
-      <c r="DO36" s="2"/>
-      <c r="DP36" s="2"/>
-      <c r="DQ36" s="2"/>
-      <c r="DR36" s="2"/>
-      <c r="DS36" s="2"/>
-      <c r="DT36" s="2"/>
-      <c r="DU36" s="2"/>
-      <c r="DV36" s="2"/>
-      <c r="DW36" s="2"/>
-      <c r="DX36" s="2"/>
-      <c r="DY36" s="2"/>
-      <c r="DZ36" s="2"/>
-      <c r="EA36" s="2"/>
-      <c r="EB36" s="2"/>
-      <c r="EC36" s="2"/>
-      <c r="ED36" s="2"/>
-      <c r="EE36" s="2"/>
-      <c r="EF36" s="2"/>
-      <c r="EG36" s="2"/>
-      <c r="EH36" s="2"/>
-      <c r="EI36" s="2"/>
-      <c r="EJ36" s="2"/>
-      <c r="EK36" s="2"/>
-      <c r="EL36" s="2"/>
-      <c r="EM36" s="2"/>
-      <c r="EN36" s="2"/>
-      <c r="EO36" s="2"/>
-      <c r="EP36" s="2"/>
-      <c r="EQ36" s="2"/>
-      <c r="ER36" s="2"/>
-      <c r="ES36" s="2"/>
-      <c r="ET36" s="2"/>
-      <c r="EU36" s="2"/>
-      <c r="EV36" s="2"/>
-      <c r="EW36" s="2"/>
-      <c r="EX36" s="2"/>
-      <c r="EY36" s="2"/>
-      <c r="EZ36" s="2"/>
-      <c r="FA36" s="2"/>
-      <c r="FB36" s="2"/>
-      <c r="FC36" s="2"/>
-      <c r="FD36" s="2"/>
-      <c r="FE36" s="2"/>
-      <c r="FF36" s="2"/>
-      <c r="FG36" s="2"/>
-      <c r="FH36" s="2"/>
-      <c r="FI36" s="2"/>
-      <c r="FJ36" s="2"/>
-      <c r="FK36" s="2"/>
-      <c r="FL36" s="2"/>
-      <c r="FM36" s="2"/>
-      <c r="FN36" s="2"/>
-      <c r="FO36" s="2"/>
-      <c r="FP36" s="2"/>
-      <c r="FQ36" s="2"/>
-      <c r="FR36" s="2"/>
-      <c r="FS36" s="2"/>
-      <c r="FT36" s="2"/>
-      <c r="FU36" s="2"/>
-      <c r="FV36" s="2"/>
-      <c r="FW36" s="2"/>
-      <c r="FX36" s="2"/>
-      <c r="FY36" s="2"/>
-      <c r="FZ36" s="2"/>
-      <c r="GA36" s="2"/>
-      <c r="GB36" s="2"/>
-      <c r="GC36" s="2"/>
-      <c r="GD36" s="2"/>
-      <c r="GE36" s="2"/>
-      <c r="GF36" s="2"/>
-      <c r="GG36" s="2"/>
-      <c r="GH36" s="2"/>
-      <c r="GI36" s="2"/>
-      <c r="GJ36" s="2"/>
-      <c r="GK36" s="2"/>
-      <c r="GL36" s="2"/>
-      <c r="GM36" s="2"/>
-      <c r="GN36" s="2"/>
-      <c r="GO36" s="2"/>
-      <c r="GP36" s="2"/>
-      <c r="GQ36" s="2"/>
-      <c r="GR36" s="2"/>
-      <c r="GS36" s="2"/>
-      <c r="GT36" s="2"/>
-      <c r="GU36" s="2"/>
-      <c r="GV36" s="2"/>
-      <c r="GW36" s="2"/>
-      <c r="GX36" s="2"/>
-      <c r="GY36" s="2"/>
-      <c r="GZ36" s="2"/>
-      <c r="HA36" s="2"/>
-      <c r="HB36" s="2"/>
-      <c r="HC36" s="2"/>
-      <c r="HD36" s="2"/>
-      <c r="HE36" s="2"/>
-      <c r="HF36" s="2"/>
-      <c r="HG36" s="2"/>
-      <c r="HH36" s="2"/>
-      <c r="HI36" s="2"/>
-      <c r="HJ36" s="2"/>
-      <c r="HK36" s="2"/>
-      <c r="HL36" s="2"/>
-      <c r="HM36" s="2"/>
-      <c r="HN36" s="2"/>
-      <c r="HO36" s="2"/>
-      <c r="HP36" s="2"/>
-      <c r="HQ36" s="2"/>
-      <c r="HR36" s="2"/>
-      <c r="HS36" s="2"/>
-      <c r="HT36" s="2"/>
-      <c r="HU36" s="2"/>
-      <c r="HV36" s="2"/>
-      <c r="HW36" s="2"/>
-      <c r="HX36" s="2"/>
-      <c r="HY36" s="2"/>
-      <c r="HZ36" s="2"/>
-      <c r="IA36" s="2"/>
-      <c r="IB36" s="2"/>
-      <c r="IC36" s="2"/>
-      <c r="ID36" s="2"/>
-      <c r="IE36" s="2"/>
-      <c r="IF36" s="2"/>
-      <c r="IG36" s="2"/>
-      <c r="IH36" s="2"/>
-      <c r="II36" s="2"/>
-      <c r="IJ36" s="2"/>
-      <c r="IK36" s="2"/>
-      <c r="IL36" s="2"/>
-      <c r="IM36" s="2"/>
-      <c r="IN36" s="2"/>
-      <c r="IO36" s="2"/>
-      <c r="IP36" s="2"/>
-      <c r="IQ36" s="2"/>
-      <c r="IR36" s="2"/>
-      <c r="IS36" s="2"/>
-      <c r="IT36" s="2"/>
-      <c r="IU36" s="2"/>
-      <c r="IV36" s="2"/>
-    </row>
-    <row r="37" spans="1:256" x14ac:dyDescent="0.35">
-      <c r="A37" s="44"/>
-      <c r="C37" s="45" t="s">
+      <c r="I38" s="2"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+      <c r="Y38" s="2"/>
+      <c r="Z38" s="2"/>
+      <c r="AA38" s="2"/>
+      <c r="AB38" s="2"/>
+      <c r="AC38" s="2"/>
+      <c r="AD38" s="2"/>
+      <c r="AE38" s="2"/>
+      <c r="AF38" s="2"/>
+      <c r="AG38" s="2"/>
+      <c r="AH38" s="2"/>
+      <c r="AI38" s="2"/>
+      <c r="AJ38" s="2"/>
+      <c r="AK38" s="2"/>
+      <c r="AL38" s="2"/>
+      <c r="AM38" s="2"/>
+      <c r="AN38" s="2"/>
+      <c r="AO38" s="2"/>
+      <c r="AP38" s="2"/>
+      <c r="AQ38" s="2"/>
+      <c r="AR38" s="2"/>
+      <c r="AS38" s="2"/>
+      <c r="AT38" s="2"/>
+      <c r="AU38" s="2"/>
+      <c r="AV38" s="2"/>
+      <c r="AW38" s="2"/>
+      <c r="AX38" s="2"/>
+      <c r="AY38" s="2"/>
+      <c r="AZ38" s="2"/>
+      <c r="BA38" s="2"/>
+      <c r="BB38" s="2"/>
+      <c r="BC38" s="2"/>
+      <c r="BD38" s="2"/>
+      <c r="BE38" s="2"/>
+      <c r="BF38" s="2"/>
+      <c r="BG38" s="2"/>
+      <c r="BH38" s="2"/>
+      <c r="BI38" s="2"/>
+      <c r="BJ38" s="2"/>
+      <c r="BK38" s="2"/>
+      <c r="BL38" s="2"/>
+      <c r="BM38" s="2"/>
+      <c r="BN38" s="2"/>
+      <c r="BO38" s="2"/>
+      <c r="BP38" s="2"/>
+      <c r="BQ38" s="2"/>
+      <c r="BR38" s="2"/>
+      <c r="BS38" s="2"/>
+      <c r="BT38" s="2"/>
+      <c r="BU38" s="2"/>
+      <c r="BV38" s="2"/>
+      <c r="BW38" s="2"/>
+      <c r="BX38" s="2"/>
+      <c r="BY38" s="2"/>
+      <c r="BZ38" s="2"/>
+      <c r="CA38" s="2"/>
+      <c r="CB38" s="2"/>
+      <c r="CC38" s="2"/>
+      <c r="CD38" s="2"/>
+      <c r="CE38" s="2"/>
+      <c r="CF38" s="2"/>
+      <c r="CG38" s="2"/>
+      <c r="CH38" s="2"/>
+      <c r="CI38" s="2"/>
+      <c r="CJ38" s="2"/>
+      <c r="CK38" s="2"/>
+      <c r="CL38" s="2"/>
+      <c r="CM38" s="2"/>
+      <c r="CN38" s="2"/>
+      <c r="CO38" s="2"/>
+      <c r="CP38" s="2"/>
+      <c r="CQ38" s="2"/>
+      <c r="CR38" s="2"/>
+      <c r="CS38" s="2"/>
+      <c r="CT38" s="2"/>
+      <c r="CU38" s="2"/>
+      <c r="CV38" s="2"/>
+      <c r="CW38" s="2"/>
+      <c r="CX38" s="2"/>
+      <c r="CY38" s="2"/>
+      <c r="CZ38" s="2"/>
+      <c r="DA38" s="2"/>
+      <c r="DB38" s="2"/>
+      <c r="DC38" s="2"/>
+      <c r="DD38" s="2"/>
+      <c r="DE38" s="2"/>
+      <c r="DF38" s="2"/>
+      <c r="DG38" s="2"/>
+      <c r="DH38" s="2"/>
+      <c r="DI38" s="2"/>
+      <c r="DJ38" s="2"/>
+      <c r="DK38" s="2"/>
+      <c r="DL38" s="2"/>
+      <c r="DM38" s="2"/>
+      <c r="DN38" s="2"/>
+      <c r="DO38" s="2"/>
+      <c r="DP38" s="2"/>
+      <c r="DQ38" s="2"/>
+      <c r="DR38" s="2"/>
+      <c r="DS38" s="2"/>
+      <c r="DT38" s="2"/>
+      <c r="DU38" s="2"/>
+      <c r="DV38" s="2"/>
+      <c r="DW38" s="2"/>
+      <c r="DX38" s="2"/>
+      <c r="DY38" s="2"/>
+      <c r="DZ38" s="2"/>
+      <c r="EA38" s="2"/>
+      <c r="EB38" s="2"/>
+      <c r="EC38" s="2"/>
+      <c r="ED38" s="2"/>
+      <c r="EE38" s="2"/>
+      <c r="EF38" s="2"/>
+      <c r="EG38" s="2"/>
+      <c r="EH38" s="2"/>
+      <c r="EI38" s="2"/>
+      <c r="EJ38" s="2"/>
+      <c r="EK38" s="2"/>
+      <c r="EL38" s="2"/>
+      <c r="EM38" s="2"/>
+      <c r="EN38" s="2"/>
+      <c r="EO38" s="2"/>
+      <c r="EP38" s="2"/>
+      <c r="EQ38" s="2"/>
+      <c r="ER38" s="2"/>
+      <c r="ES38" s="2"/>
+      <c r="ET38" s="2"/>
+      <c r="EU38" s="2"/>
+      <c r="EV38" s="2"/>
+      <c r="EW38" s="2"/>
+      <c r="EX38" s="2"/>
+      <c r="EY38" s="2"/>
+      <c r="EZ38" s="2"/>
+      <c r="FA38" s="2"/>
+      <c r="FB38" s="2"/>
+      <c r="FC38" s="2"/>
+      <c r="FD38" s="2"/>
+      <c r="FE38" s="2"/>
+      <c r="FF38" s="2"/>
+      <c r="FG38" s="2"/>
+      <c r="FH38" s="2"/>
+      <c r="FI38" s="2"/>
+      <c r="FJ38" s="2"/>
+      <c r="FK38" s="2"/>
+      <c r="FL38" s="2"/>
+      <c r="FM38" s="2"/>
+      <c r="FN38" s="2"/>
+      <c r="FO38" s="2"/>
+      <c r="FP38" s="2"/>
+      <c r="FQ38" s="2"/>
+      <c r="FR38" s="2"/>
+      <c r="FS38" s="2"/>
+      <c r="FT38" s="2"/>
+      <c r="FU38" s="2"/>
+      <c r="FV38" s="2"/>
+      <c r="FW38" s="2"/>
+      <c r="FX38" s="2"/>
+      <c r="FY38" s="2"/>
+      <c r="FZ38" s="2"/>
+      <c r="GA38" s="2"/>
+      <c r="GB38" s="2"/>
+      <c r="GC38" s="2"/>
+      <c r="GD38" s="2"/>
+      <c r="GE38" s="2"/>
+      <c r="GF38" s="2"/>
+      <c r="GG38" s="2"/>
+      <c r="GH38" s="2"/>
+      <c r="GI38" s="2"/>
+      <c r="GJ38" s="2"/>
+      <c r="GK38" s="2"/>
+      <c r="GL38" s="2"/>
+      <c r="GM38" s="2"/>
+      <c r="GN38" s="2"/>
+      <c r="GO38" s="2"/>
+      <c r="GP38" s="2"/>
+      <c r="GQ38" s="2"/>
+      <c r="GR38" s="2"/>
+      <c r="GS38" s="2"/>
+      <c r="GT38" s="2"/>
+      <c r="GU38" s="2"/>
+      <c r="GV38" s="2"/>
+      <c r="GW38" s="2"/>
+      <c r="GX38" s="2"/>
+      <c r="GY38" s="2"/>
+      <c r="GZ38" s="2"/>
+      <c r="HA38" s="2"/>
+      <c r="HB38" s="2"/>
+      <c r="HC38" s="2"/>
+      <c r="HD38" s="2"/>
+      <c r="HE38" s="2"/>
+      <c r="HF38" s="2"/>
+      <c r="HG38" s="2"/>
+      <c r="HH38" s="2"/>
+      <c r="HI38" s="2"/>
+      <c r="HJ38" s="2"/>
+      <c r="HK38" s="2"/>
+      <c r="HL38" s="2"/>
+      <c r="HM38" s="2"/>
+      <c r="HN38" s="2"/>
+      <c r="HO38" s="2"/>
+      <c r="HP38" s="2"/>
+      <c r="HQ38" s="2"/>
+      <c r="HR38" s="2"/>
+      <c r="HS38" s="2"/>
+      <c r="HT38" s="2"/>
+      <c r="HU38" s="2"/>
+      <c r="HV38" s="2"/>
+      <c r="HW38" s="2"/>
+      <c r="HX38" s="2"/>
+      <c r="HY38" s="2"/>
+      <c r="HZ38" s="2"/>
+      <c r="IA38" s="2"/>
+      <c r="IB38" s="2"/>
+      <c r="IC38" s="2"/>
+      <c r="ID38" s="2"/>
+      <c r="IE38" s="2"/>
+      <c r="IF38" s="2"/>
+      <c r="IG38" s="2"/>
+      <c r="IH38" s="2"/>
+      <c r="II38" s="2"/>
+      <c r="IJ38" s="2"/>
+      <c r="IK38" s="2"/>
+      <c r="IL38" s="2"/>
+      <c r="IM38" s="2"/>
+      <c r="IN38" s="2"/>
+      <c r="IO38" s="2"/>
+      <c r="IP38" s="2"/>
+      <c r="IQ38" s="2"/>
+      <c r="IR38" s="2"/>
+      <c r="IS38" s="2"/>
+      <c r="IT38" s="2"/>
+      <c r="IU38" s="2"/>
+      <c r="IV38" s="2"/>
+    </row>
+    <row r="39" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="A39" s="24"/>
+      <c r="C39" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D37" s="46"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="47"/>
-      <c r="J37" s="44"/>
-    </row>
-    <row r="38" spans="1:256" x14ac:dyDescent="0.35">
-      <c r="A38" s="44"/>
-      <c r="C38" s="48" t="s">
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="27"/>
+      <c r="J39" s="24"/>
+    </row>
+    <row r="40" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+      <c r="C40" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="51" t="s">
+      <c r="D40" s="86"/>
+      <c r="E40" s="86"/>
+      <c r="F40" s="87"/>
+      <c r="G40" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H38" s="52"/>
-      <c r="J38" s="44"/>
-    </row>
-    <row r="39" spans="1:256" x14ac:dyDescent="0.35">
-      <c r="A39" s="44"/>
-      <c r="C39" s="53" t="s">
+      <c r="H40" s="29"/>
+      <c r="J40" s="24"/>
+    </row>
+    <row r="41" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="A41" s="24"/>
+      <c r="C41" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="D39" s="54"/>
-      <c r="E39" s="133" t="s">
+      <c r="D41" s="68"/>
+      <c r="E41" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="F39" s="134"/>
-      <c r="G39" s="55" t="s">
+      <c r="F41" s="70"/>
+      <c r="G41" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="H39" s="52"/>
-      <c r="J39" s="44"/>
-    </row>
-    <row r="40" spans="1:256" x14ac:dyDescent="0.35">
-      <c r="A40" s="44"/>
-      <c r="C40" s="53" t="s">
+      <c r="H41" s="29"/>
+      <c r="J41" s="24"/>
+    </row>
+    <row r="42" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="A42" s="24"/>
+      <c r="C42" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="54"/>
-      <c r="E40" s="133" t="s">
+      <c r="D42" s="68"/>
+      <c r="E42" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="F40" s="134"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="52"/>
-      <c r="J40" s="44"/>
-    </row>
-    <row r="41" spans="1:256" x14ac:dyDescent="0.35">
-      <c r="A41" s="44"/>
-      <c r="C41" s="53" t="s">
+      <c r="F42" s="70"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="29"/>
+      <c r="J42" s="24"/>
+    </row>
+    <row r="43" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="A43" s="24"/>
+      <c r="C43" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="54"/>
-      <c r="E41" s="133" t="s">
+      <c r="D43" s="68"/>
+      <c r="E43" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="F41" s="134"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="52"/>
-      <c r="J41" s="44"/>
-    </row>
-    <row r="42" spans="1:256" x14ac:dyDescent="0.35">
-      <c r="A42" s="44"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="59"/>
-      <c r="H42" s="52"/>
-      <c r="J42" s="44"/>
-    </row>
-    <row r="43" spans="1:256" x14ac:dyDescent="0.35">
-      <c r="A43" s="44"/>
-      <c r="C43" s="48" t="s">
+      <c r="F43" s="70"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="29"/>
+      <c r="J43" s="24"/>
+    </row>
+    <row r="44" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="A44" s="24"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="29"/>
+      <c r="J44" s="24"/>
+    </row>
+    <row r="45" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="A45" s="24"/>
+      <c r="C45" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="51" t="s">
+      <c r="D45" s="86"/>
+      <c r="E45" s="86"/>
+      <c r="F45" s="87"/>
+      <c r="G45" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H43" s="52"/>
-      <c r="J43" s="44"/>
-    </row>
-    <row r="44" spans="1:256" x14ac:dyDescent="0.35">
-      <c r="A44" s="44"/>
-      <c r="C44" s="53" t="s">
+      <c r="H45" s="29"/>
+      <c r="J45" s="24"/>
+    </row>
+    <row r="46" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="A46" s="24"/>
+      <c r="C46" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="D44" s="54"/>
-      <c r="E44" s="133" t="s">
+      <c r="D46" s="68"/>
+      <c r="E46" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="F44" s="134"/>
-      <c r="G44" s="55" t="s">
+      <c r="F46" s="70"/>
+      <c r="G46" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="H44" s="52"/>
-      <c r="J44" s="44"/>
-    </row>
-    <row r="45" spans="1:256" x14ac:dyDescent="0.35">
-      <c r="A45" s="44"/>
-      <c r="C45" s="53" t="s">
+      <c r="H46" s="29"/>
+      <c r="J46" s="24"/>
+    </row>
+    <row r="47" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="A47" s="24"/>
+      <c r="C47" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="D45" s="54"/>
-      <c r="E45" s="133" t="s">
+      <c r="D47" s="68"/>
+      <c r="E47" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="F45" s="134"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="52"/>
-      <c r="J45" s="44"/>
-    </row>
-    <row r="46" spans="1:256" x14ac:dyDescent="0.35">
-      <c r="A46" s="44"/>
-      <c r="C46" s="53" t="s">
+      <c r="F47" s="70"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="29"/>
+      <c r="J47" s="24"/>
+    </row>
+    <row r="48" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="A48" s="24"/>
+      <c r="C48" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="D46" s="54"/>
-      <c r="E46" s="133" t="s">
+      <c r="D48" s="68"/>
+      <c r="E48" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="F46" s="134"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="52"/>
-      <c r="J46" s="44"/>
-    </row>
-    <row r="47" spans="1:256" x14ac:dyDescent="0.35">
-      <c r="A47" s="1"/>
-      <c r="C47" s="53" t="s">
+      <c r="F48" s="70"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="29"/>
+      <c r="J48" s="24"/>
+    </row>
+    <row r="49" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="C49" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="D47" s="54"/>
-      <c r="E47" s="133" t="s">
+      <c r="D49" s="68"/>
+      <c r="E49" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="F47" s="134"/>
-      <c r="G47" s="56"/>
-      <c r="H47" s="52"/>
-      <c r="J47" s="1"/>
-    </row>
-    <row r="48" spans="1:256" x14ac:dyDescent="0.35">
-      <c r="A48" s="1"/>
-      <c r="C48" s="53" t="s">
+      <c r="F49" s="70"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="29"/>
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="C50" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="D48" s="54"/>
-      <c r="E48" s="135" t="s">
+      <c r="D50" s="68"/>
+      <c r="E50" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="F48" s="136"/>
-      <c r="G48" s="55" t="s">
+      <c r="F50" s="72"/>
+      <c r="G50" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="H48" s="52"/>
-      <c r="J48" s="1"/>
-    </row>
-    <row r="49" spans="1:256" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="1"/>
-      <c r="C49" s="60"/>
-      <c r="D49" s="61"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="62"/>
-      <c r="G49" s="63"/>
-      <c r="H49" s="64"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="1"/>
-      <c r="C50" s="65" t="s">
+      <c r="H50" s="29"/>
+      <c r="J50" s="1"/>
+    </row>
+    <row r="51" spans="1:256" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+      <c r="C51" s="35"/>
+      <c r="D51" s="36"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="39"/>
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="C52" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="D50" s="66"/>
-      <c r="E50" s="66"/>
-      <c r="F50" s="66"/>
-      <c r="G50" s="66"/>
-      <c r="H50" s="67"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="2"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="2"/>
-      <c r="T50" s="2"/>
-      <c r="U50" s="2"/>
-      <c r="V50" s="2"/>
-      <c r="W50" s="2"/>
-      <c r="X50" s="2"/>
-      <c r="Y50" s="2"/>
-      <c r="Z50" s="2"/>
-      <c r="AA50" s="2"/>
-      <c r="AB50" s="2"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="2"/>
-      <c r="AE50" s="2"/>
-      <c r="AF50" s="2"/>
-      <c r="AG50" s="2"/>
-      <c r="AH50" s="2"/>
-      <c r="AI50" s="2"/>
-      <c r="AJ50" s="2"/>
-      <c r="AK50" s="2"/>
-      <c r="AL50" s="2"/>
-      <c r="AM50" s="2"/>
-      <c r="AN50" s="2"/>
-      <c r="AO50" s="2"/>
-      <c r="AP50" s="2"/>
-      <c r="AQ50" s="2"/>
-      <c r="AR50" s="2"/>
-      <c r="AS50" s="2"/>
-      <c r="AT50" s="2"/>
-      <c r="AU50" s="2"/>
-      <c r="AV50" s="2"/>
-      <c r="AW50" s="2"/>
-      <c r="AX50" s="2"/>
-      <c r="AY50" s="2"/>
-      <c r="AZ50" s="2"/>
-      <c r="BA50" s="2"/>
-      <c r="BB50" s="2"/>
-      <c r="BC50" s="2"/>
-      <c r="BD50" s="2"/>
-      <c r="BE50" s="2"/>
-      <c r="BF50" s="2"/>
-      <c r="BG50" s="2"/>
-      <c r="BH50" s="2"/>
-      <c r="BI50" s="2"/>
-      <c r="BJ50" s="2"/>
-      <c r="BK50" s="2"/>
-      <c r="BL50" s="2"/>
-      <c r="BM50" s="2"/>
-      <c r="BN50" s="2"/>
-      <c r="BO50" s="2"/>
-      <c r="BP50" s="2"/>
-      <c r="BQ50" s="2"/>
-      <c r="BR50" s="2"/>
-      <c r="BS50" s="2"/>
-      <c r="BT50" s="2"/>
-      <c r="BU50" s="2"/>
-      <c r="BV50" s="2"/>
-      <c r="BW50" s="2"/>
-      <c r="BX50" s="2"/>
-      <c r="BY50" s="2"/>
-      <c r="BZ50" s="2"/>
-      <c r="CA50" s="2"/>
-      <c r="CB50" s="2"/>
-      <c r="CC50" s="2"/>
-      <c r="CD50" s="2"/>
-      <c r="CE50" s="2"/>
-      <c r="CF50" s="2"/>
-      <c r="CG50" s="2"/>
-      <c r="CH50" s="2"/>
-      <c r="CI50" s="2"/>
-      <c r="CJ50" s="2"/>
-      <c r="CK50" s="2"/>
-      <c r="CL50" s="2"/>
-      <c r="CM50" s="2"/>
-      <c r="CN50" s="2"/>
-      <c r="CO50" s="2"/>
-      <c r="CP50" s="2"/>
-      <c r="CQ50" s="2"/>
-      <c r="CR50" s="2"/>
-      <c r="CS50" s="2"/>
-      <c r="CT50" s="2"/>
-      <c r="CU50" s="2"/>
-      <c r="CV50" s="2"/>
-      <c r="CW50" s="2"/>
-      <c r="CX50" s="2"/>
-      <c r="CY50" s="2"/>
-      <c r="CZ50" s="2"/>
-      <c r="DA50" s="2"/>
-      <c r="DB50" s="2"/>
-      <c r="DC50" s="2"/>
-      <c r="DD50" s="2"/>
-      <c r="DE50" s="2"/>
-      <c r="DF50" s="2"/>
-      <c r="DG50" s="2"/>
-      <c r="DH50" s="2"/>
-      <c r="DI50" s="2"/>
-      <c r="DJ50" s="2"/>
-      <c r="DK50" s="2"/>
-      <c r="DL50" s="2"/>
-      <c r="DM50" s="2"/>
-      <c r="DN50" s="2"/>
-      <c r="DO50" s="2"/>
-      <c r="DP50" s="2"/>
-      <c r="DQ50" s="2"/>
-      <c r="DR50" s="2"/>
-      <c r="DS50" s="2"/>
-      <c r="DT50" s="2"/>
-      <c r="DU50" s="2"/>
-      <c r="DV50" s="2"/>
-      <c r="DW50" s="2"/>
-      <c r="DX50" s="2"/>
-      <c r="DY50" s="2"/>
-      <c r="DZ50" s="2"/>
-      <c r="EA50" s="2"/>
-      <c r="EB50" s="2"/>
-      <c r="EC50" s="2"/>
-      <c r="ED50" s="2"/>
-      <c r="EE50" s="2"/>
-      <c r="EF50" s="2"/>
-      <c r="EG50" s="2"/>
-      <c r="EH50" s="2"/>
-      <c r="EI50" s="2"/>
-      <c r="EJ50" s="2"/>
-      <c r="EK50" s="2"/>
-      <c r="EL50" s="2"/>
-      <c r="EM50" s="2"/>
-      <c r="EN50" s="2"/>
-      <c r="EO50" s="2"/>
-      <c r="EP50" s="2"/>
-      <c r="EQ50" s="2"/>
-      <c r="ER50" s="2"/>
-      <c r="ES50" s="2"/>
-      <c r="ET50" s="2"/>
-      <c r="EU50" s="2"/>
-      <c r="EV50" s="2"/>
-      <c r="EW50" s="2"/>
-      <c r="EX50" s="2"/>
-      <c r="EY50" s="2"/>
-      <c r="EZ50" s="2"/>
-      <c r="FA50" s="2"/>
-      <c r="FB50" s="2"/>
-      <c r="FC50" s="2"/>
-      <c r="FD50" s="2"/>
-      <c r="FE50" s="2"/>
-      <c r="FF50" s="2"/>
-      <c r="FG50" s="2"/>
-      <c r="FH50" s="2"/>
-      <c r="FI50" s="2"/>
-      <c r="FJ50" s="2"/>
-      <c r="FK50" s="2"/>
-      <c r="FL50" s="2"/>
-      <c r="FM50" s="2"/>
-      <c r="FN50" s="2"/>
-      <c r="FO50" s="2"/>
-      <c r="FP50" s="2"/>
-      <c r="FQ50" s="2"/>
-      <c r="FR50" s="2"/>
-      <c r="FS50" s="2"/>
-      <c r="FT50" s="2"/>
-      <c r="FU50" s="2"/>
-      <c r="FV50" s="2"/>
-      <c r="FW50" s="2"/>
-      <c r="FX50" s="2"/>
-      <c r="FY50" s="2"/>
-      <c r="FZ50" s="2"/>
-      <c r="GA50" s="2"/>
-      <c r="GB50" s="2"/>
-      <c r="GC50" s="2"/>
-      <c r="GD50" s="2"/>
-      <c r="GE50" s="2"/>
-      <c r="GF50" s="2"/>
-      <c r="GG50" s="2"/>
-      <c r="GH50" s="2"/>
-      <c r="GI50" s="2"/>
-      <c r="GJ50" s="2"/>
-      <c r="GK50" s="2"/>
-      <c r="GL50" s="2"/>
-      <c r="GM50" s="2"/>
-      <c r="GN50" s="2"/>
-      <c r="GO50" s="2"/>
-      <c r="GP50" s="2"/>
-      <c r="GQ50" s="2"/>
-      <c r="GR50" s="2"/>
-      <c r="GS50" s="2"/>
-      <c r="GT50" s="2"/>
-      <c r="GU50" s="2"/>
-      <c r="GV50" s="2"/>
-      <c r="GW50" s="2"/>
-      <c r="GX50" s="2"/>
-      <c r="GY50" s="2"/>
-      <c r="GZ50" s="2"/>
-      <c r="HA50" s="2"/>
-      <c r="HB50" s="2"/>
-      <c r="HC50" s="2"/>
-      <c r="HD50" s="2"/>
-      <c r="HE50" s="2"/>
-      <c r="HF50" s="2"/>
-      <c r="HG50" s="2"/>
-      <c r="HH50" s="2"/>
-      <c r="HI50" s="2"/>
-      <c r="HJ50" s="2"/>
-      <c r="HK50" s="2"/>
-      <c r="HL50" s="2"/>
-      <c r="HM50" s="2"/>
-      <c r="HN50" s="2"/>
-      <c r="HO50" s="2"/>
-      <c r="HP50" s="2"/>
-      <c r="HQ50" s="2"/>
-      <c r="HR50" s="2"/>
-      <c r="HS50" s="2"/>
-      <c r="HT50" s="2"/>
-      <c r="HU50" s="2"/>
-      <c r="HV50" s="2"/>
-      <c r="HW50" s="2"/>
-      <c r="HX50" s="2"/>
-      <c r="HY50" s="2"/>
-      <c r="HZ50" s="2"/>
-      <c r="IA50" s="2"/>
-      <c r="IB50" s="2"/>
-      <c r="IC50" s="2"/>
-      <c r="ID50" s="2"/>
-      <c r="IE50" s="2"/>
-      <c r="IF50" s="2"/>
-      <c r="IG50" s="2"/>
-      <c r="IH50" s="2"/>
-      <c r="II50" s="2"/>
-      <c r="IJ50" s="2"/>
-      <c r="IK50" s="2"/>
-      <c r="IL50" s="2"/>
-      <c r="IM50" s="2"/>
-      <c r="IN50" s="2"/>
-      <c r="IO50" s="2"/>
-      <c r="IP50" s="2"/>
-      <c r="IQ50" s="2"/>
-      <c r="IR50" s="2"/>
-      <c r="IS50" s="2"/>
-      <c r="IT50" s="2"/>
-      <c r="IU50" s="2"/>
-      <c r="IV50" s="2"/>
-    </row>
-    <row r="51" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="1"/>
-      <c r="C51" s="68" t="s">
-        <v>43</v>
-      </c>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="69"/>
-      <c r="H51" s="70"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="2"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="2"/>
-      <c r="T51" s="2"/>
-      <c r="U51" s="2"/>
-      <c r="V51" s="2"/>
-      <c r="W51" s="2"/>
-      <c r="X51" s="2"/>
-      <c r="Y51" s="2"/>
-      <c r="Z51" s="2"/>
-      <c r="AA51" s="2"/>
-      <c r="AB51" s="2"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="2"/>
-      <c r="AE51" s="2"/>
-      <c r="AF51" s="2"/>
-      <c r="AG51" s="2"/>
-      <c r="AH51" s="2"/>
-      <c r="AI51" s="2"/>
-      <c r="AJ51" s="2"/>
-      <c r="AK51" s="2"/>
-      <c r="AL51" s="2"/>
-      <c r="AM51" s="2"/>
-      <c r="AN51" s="2"/>
-      <c r="AO51" s="2"/>
-      <c r="AP51" s="2"/>
-      <c r="AQ51" s="2"/>
-      <c r="AR51" s="2"/>
-      <c r="AS51" s="2"/>
-      <c r="AT51" s="2"/>
-      <c r="AU51" s="2"/>
-      <c r="AV51" s="2"/>
-      <c r="AW51" s="2"/>
-      <c r="AX51" s="2"/>
-      <c r="AY51" s="2"/>
-      <c r="AZ51" s="2"/>
-      <c r="BA51" s="2"/>
-      <c r="BB51" s="2"/>
-      <c r="BC51" s="2"/>
-      <c r="BD51" s="2"/>
-      <c r="BE51" s="2"/>
-      <c r="BF51" s="2"/>
-      <c r="BG51" s="2"/>
-      <c r="BH51" s="2"/>
-      <c r="BI51" s="2"/>
-      <c r="BJ51" s="2"/>
-      <c r="BK51" s="2"/>
-      <c r="BL51" s="2"/>
-      <c r="BM51" s="2"/>
-      <c r="BN51" s="2"/>
-      <c r="BO51" s="2"/>
-      <c r="BP51" s="2"/>
-      <c r="BQ51" s="2"/>
-      <c r="BR51" s="2"/>
-      <c r="BS51" s="2"/>
-      <c r="BT51" s="2"/>
-      <c r="BU51" s="2"/>
-      <c r="BV51" s="2"/>
-      <c r="BW51" s="2"/>
-      <c r="BX51" s="2"/>
-      <c r="BY51" s="2"/>
-      <c r="BZ51" s="2"/>
-      <c r="CA51" s="2"/>
-      <c r="CB51" s="2"/>
-      <c r="CC51" s="2"/>
-      <c r="CD51" s="2"/>
-      <c r="CE51" s="2"/>
-      <c r="CF51" s="2"/>
-      <c r="CG51" s="2"/>
-      <c r="CH51" s="2"/>
-      <c r="CI51" s="2"/>
-      <c r="CJ51" s="2"/>
-      <c r="CK51" s="2"/>
-      <c r="CL51" s="2"/>
-      <c r="CM51" s="2"/>
-      <c r="CN51" s="2"/>
-      <c r="CO51" s="2"/>
-      <c r="CP51" s="2"/>
-      <c r="CQ51" s="2"/>
-      <c r="CR51" s="2"/>
-      <c r="CS51" s="2"/>
-      <c r="CT51" s="2"/>
-      <c r="CU51" s="2"/>
-      <c r="CV51" s="2"/>
-      <c r="CW51" s="2"/>
-      <c r="CX51" s="2"/>
-      <c r="CY51" s="2"/>
-      <c r="CZ51" s="2"/>
-      <c r="DA51" s="2"/>
-      <c r="DB51" s="2"/>
-      <c r="DC51" s="2"/>
-      <c r="DD51" s="2"/>
-      <c r="DE51" s="2"/>
-      <c r="DF51" s="2"/>
-      <c r="DG51" s="2"/>
-      <c r="DH51" s="2"/>
-      <c r="DI51" s="2"/>
-      <c r="DJ51" s="2"/>
-      <c r="DK51" s="2"/>
-      <c r="DL51" s="2"/>
-      <c r="DM51" s="2"/>
-      <c r="DN51" s="2"/>
-      <c r="DO51" s="2"/>
-      <c r="DP51" s="2"/>
-      <c r="DQ51" s="2"/>
-      <c r="DR51" s="2"/>
-      <c r="DS51" s="2"/>
-      <c r="DT51" s="2"/>
-      <c r="DU51" s="2"/>
-      <c r="DV51" s="2"/>
-      <c r="DW51" s="2"/>
-      <c r="DX51" s="2"/>
-      <c r="DY51" s="2"/>
-      <c r="DZ51" s="2"/>
-      <c r="EA51" s="2"/>
-      <c r="EB51" s="2"/>
-      <c r="EC51" s="2"/>
-      <c r="ED51" s="2"/>
-      <c r="EE51" s="2"/>
-      <c r="EF51" s="2"/>
-      <c r="EG51" s="2"/>
-      <c r="EH51" s="2"/>
-      <c r="EI51" s="2"/>
-      <c r="EJ51" s="2"/>
-      <c r="EK51" s="2"/>
-      <c r="EL51" s="2"/>
-      <c r="EM51" s="2"/>
-      <c r="EN51" s="2"/>
-      <c r="EO51" s="2"/>
-      <c r="EP51" s="2"/>
-      <c r="EQ51" s="2"/>
-      <c r="ER51" s="2"/>
-      <c r="ES51" s="2"/>
-      <c r="ET51" s="2"/>
-      <c r="EU51" s="2"/>
-      <c r="EV51" s="2"/>
-      <c r="EW51" s="2"/>
-      <c r="EX51" s="2"/>
-      <c r="EY51" s="2"/>
-      <c r="EZ51" s="2"/>
-      <c r="FA51" s="2"/>
-      <c r="FB51" s="2"/>
-      <c r="FC51" s="2"/>
-      <c r="FD51" s="2"/>
-      <c r="FE51" s="2"/>
-      <c r="FF51" s="2"/>
-      <c r="FG51" s="2"/>
-      <c r="FH51" s="2"/>
-      <c r="FI51" s="2"/>
-      <c r="FJ51" s="2"/>
-      <c r="FK51" s="2"/>
-      <c r="FL51" s="2"/>
-      <c r="FM51" s="2"/>
-      <c r="FN51" s="2"/>
-      <c r="FO51" s="2"/>
-      <c r="FP51" s="2"/>
-      <c r="FQ51" s="2"/>
-      <c r="FR51" s="2"/>
-      <c r="FS51" s="2"/>
-      <c r="FT51" s="2"/>
-      <c r="FU51" s="2"/>
-      <c r="FV51" s="2"/>
-      <c r="FW51" s="2"/>
-      <c r="FX51" s="2"/>
-      <c r="FY51" s="2"/>
-      <c r="FZ51" s="2"/>
-      <c r="GA51" s="2"/>
-      <c r="GB51" s="2"/>
-      <c r="GC51" s="2"/>
-      <c r="GD51" s="2"/>
-      <c r="GE51" s="2"/>
-      <c r="GF51" s="2"/>
-      <c r="GG51" s="2"/>
-      <c r="GH51" s="2"/>
-      <c r="GI51" s="2"/>
-      <c r="GJ51" s="2"/>
-      <c r="GK51" s="2"/>
-      <c r="GL51" s="2"/>
-      <c r="GM51" s="2"/>
-      <c r="GN51" s="2"/>
-      <c r="GO51" s="2"/>
-      <c r="GP51" s="2"/>
-      <c r="GQ51" s="2"/>
-      <c r="GR51" s="2"/>
-      <c r="GS51" s="2"/>
-      <c r="GT51" s="2"/>
-      <c r="GU51" s="2"/>
-      <c r="GV51" s="2"/>
-      <c r="GW51" s="2"/>
-      <c r="GX51" s="2"/>
-      <c r="GY51" s="2"/>
-      <c r="GZ51" s="2"/>
-      <c r="HA51" s="2"/>
-      <c r="HB51" s="2"/>
-      <c r="HC51" s="2"/>
-      <c r="HD51" s="2"/>
-      <c r="HE51" s="2"/>
-      <c r="HF51" s="2"/>
-      <c r="HG51" s="2"/>
-      <c r="HH51" s="2"/>
-      <c r="HI51" s="2"/>
-      <c r="HJ51" s="2"/>
-      <c r="HK51" s="2"/>
-      <c r="HL51" s="2"/>
-      <c r="HM51" s="2"/>
-      <c r="HN51" s="2"/>
-      <c r="HO51" s="2"/>
-      <c r="HP51" s="2"/>
-      <c r="HQ51" s="2"/>
-      <c r="HR51" s="2"/>
-      <c r="HS51" s="2"/>
-      <c r="HT51" s="2"/>
-      <c r="HU51" s="2"/>
-      <c r="HV51" s="2"/>
-      <c r="HW51" s="2"/>
-      <c r="HX51" s="2"/>
-      <c r="HY51" s="2"/>
-      <c r="HZ51" s="2"/>
-      <c r="IA51" s="2"/>
-      <c r="IB51" s="2"/>
-      <c r="IC51" s="2"/>
-      <c r="ID51" s="2"/>
-      <c r="IE51" s="2"/>
-      <c r="IF51" s="2"/>
-      <c r="IG51" s="2"/>
-      <c r="IH51" s="2"/>
-      <c r="II51" s="2"/>
-      <c r="IJ51" s="2"/>
-      <c r="IK51" s="2"/>
-      <c r="IL51" s="2"/>
-      <c r="IM51" s="2"/>
-      <c r="IN51" s="2"/>
-      <c r="IO51" s="2"/>
-      <c r="IP51" s="2"/>
-      <c r="IQ51" s="2"/>
-      <c r="IR51" s="2"/>
-      <c r="IS51" s="2"/>
-      <c r="IT51" s="2"/>
-      <c r="IU51" s="2"/>
-      <c r="IV51" s="2"/>
-    </row>
-    <row r="52" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="1"/>
-      <c r="C52" s="71"/>
-      <c r="D52" s="72"/>
-      <c r="E52" s="72"/>
-      <c r="F52" s="72"/>
-      <c r="G52" s="72"/>
-      <c r="H52" s="73"/>
+      <c r="D52" s="74"/>
+      <c r="E52" s="74"/>
+      <c r="F52" s="74"/>
+      <c r="G52" s="74"/>
+      <c r="H52" s="75"/>
       <c r="I52" s="2"/>
       <c r="J52" s="1"/>
       <c r="K52" s="2"/>
@@ -3689,14 +3223,16 @@
       <c r="IU52" s="2"/>
       <c r="IV52" s="2"/>
     </row>
-    <row r="53" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="C53" s="71"/>
-      <c r="D53" s="72"/>
-      <c r="E53" s="72"/>
-      <c r="F53" s="72"/>
-      <c r="G53" s="72"/>
-      <c r="H53" s="73"/>
+      <c r="C53" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="D53" s="77"/>
+      <c r="E53" s="77"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="77"/>
+      <c r="H53" s="78"/>
       <c r="I53" s="2"/>
       <c r="J53" s="1"/>
       <c r="K53" s="2"/>
@@ -3946,14 +3482,14 @@
       <c r="IU53" s="2"/>
       <c r="IV53" s="2"/>
     </row>
-    <row r="54" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="C54" s="71"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="72"/>
-      <c r="F54" s="72"/>
-      <c r="G54" s="72"/>
-      <c r="H54" s="73"/>
+      <c r="C54" s="79"/>
+      <c r="D54" s="80"/>
+      <c r="E54" s="80"/>
+      <c r="F54" s="80"/>
+      <c r="G54" s="80"/>
+      <c r="H54" s="81"/>
       <c r="I54" s="2"/>
       <c r="J54" s="1"/>
       <c r="K54" s="2"/>
@@ -4203,14 +3739,14 @@
       <c r="IU54" s="2"/>
       <c r="IV54" s="2"/>
     </row>
-    <row r="55" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="C55" s="71"/>
-      <c r="D55" s="72"/>
-      <c r="E55" s="72"/>
-      <c r="F55" s="72"/>
-      <c r="G55" s="72"/>
-      <c r="H55" s="73"/>
+      <c r="C55" s="79"/>
+      <c r="D55" s="80"/>
+      <c r="E55" s="80"/>
+      <c r="F55" s="80"/>
+      <c r="G55" s="80"/>
+      <c r="H55" s="81"/>
       <c r="I55" s="2"/>
       <c r="J55" s="1"/>
       <c r="K55" s="2"/>
@@ -4460,14 +3996,14 @@
       <c r="IU55" s="2"/>
       <c r="IV55" s="2"/>
     </row>
-    <row r="56" spans="1:256" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
-      <c r="C56" s="74"/>
-      <c r="D56" s="75"/>
-      <c r="E56" s="75"/>
-      <c r="F56" s="75"/>
-      <c r="G56" s="75"/>
-      <c r="H56" s="76"/>
+      <c r="C56" s="79"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="80"/>
+      <c r="F56" s="80"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="81"/>
       <c r="I56" s="2"/>
       <c r="J56" s="1"/>
       <c r="K56" s="2"/>
@@ -4717,16 +4253,14 @@
       <c r="IU56" s="2"/>
       <c r="IV56" s="2"/>
     </row>
-    <row r="57" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="C57" s="77" t="s">
-        <v>44</v>
-      </c>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
-      <c r="F57" s="78"/>
-      <c r="G57" s="78"/>
-      <c r="H57" s="79"/>
+      <c r="C57" s="79"/>
+      <c r="D57" s="80"/>
+      <c r="E57" s="80"/>
+      <c r="F57" s="80"/>
+      <c r="G57" s="80"/>
+      <c r="H57" s="81"/>
       <c r="I57" s="2"/>
       <c r="J57" s="1"/>
       <c r="K57" s="2"/>
@@ -4976,20 +4510,14 @@
       <c r="IU57" s="2"/>
       <c r="IV57" s="2"/>
     </row>
-    <row r="58" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:256" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
-      <c r="C58" s="80" t="s">
-        <v>45</v>
-      </c>
-      <c r="D58" s="81"/>
-      <c r="E58" s="82"/>
-      <c r="F58" s="83" t="s">
-        <v>46</v>
-      </c>
-      <c r="G58" s="84" t="s">
-        <v>47</v>
-      </c>
-      <c r="H58" s="85"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="83"/>
+      <c r="E58" s="83"/>
+      <c r="F58" s="83"/>
+      <c r="G58" s="83"/>
+      <c r="H58" s="84"/>
       <c r="I58" s="2"/>
       <c r="J58" s="1"/>
       <c r="K58" s="2"/>
@@ -5239,16 +4767,16 @@
       <c r="IU58" s="2"/>
       <c r="IV58" s="2"/>
     </row>
-    <row r="59" spans="1:256" customFormat="1" ht="21.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="C59" s="86" t="s">
-        <v>48</v>
-      </c>
-      <c r="D59" s="87"/>
-      <c r="E59" s="88"/>
-      <c r="F59" s="89"/>
-      <c r="G59" s="87"/>
-      <c r="H59" s="90"/>
+      <c r="C59" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="D59" s="51"/>
+      <c r="E59" s="51"/>
+      <c r="F59" s="51"/>
+      <c r="G59" s="51"/>
+      <c r="H59" s="52"/>
       <c r="I59" s="2"/>
       <c r="J59" s="1"/>
       <c r="K59" s="2"/>
@@ -5498,21 +5026,20 @@
       <c r="IU59" s="2"/>
       <c r="IV59" s="2"/>
     </row>
-    <row r="60" spans="1:256" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
-      <c r="C60" s="91" t="str">
-        <f>E48</f>
-        <v>Yeni Roncancio</v>
-      </c>
-      <c r="D60" s="92"/>
-      <c r="E60" s="93"/>
-      <c r="F60" s="94" t="s">
-        <v>49</v>
-      </c>
-      <c r="G60" s="95" t="s">
-        <v>50</v>
-      </c>
-      <c r="H60" s="96"/>
+      <c r="C60" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="D60" s="54"/>
+      <c r="E60" s="55"/>
+      <c r="F60" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="G60" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="H60" s="42"/>
       <c r="I60" s="2"/>
       <c r="J60" s="1"/>
       <c r="K60" s="2"/>
@@ -5762,16 +5289,16 @@
       <c r="IU60" s="2"/>
       <c r="IV60" s="2"/>
     </row>
-    <row r="61" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:256" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="C61" s="97" t="s">
-        <v>51</v>
-      </c>
-      <c r="D61" s="98"/>
-      <c r="E61" s="98"/>
-      <c r="F61" s="98"/>
-      <c r="G61" s="98"/>
-      <c r="H61" s="99"/>
+      <c r="C61" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="44"/>
+      <c r="E61" s="45"/>
+      <c r="F61" s="46"/>
+      <c r="G61" s="44"/>
+      <c r="H61" s="47"/>
       <c r="I61" s="2"/>
       <c r="J61" s="1"/>
       <c r="K61" s="2"/>
@@ -6021,16 +5548,21 @@
       <c r="IU61" s="2"/>
       <c r="IV61" s="2"/>
     </row>
-    <row r="62" spans="1:256" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:256" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
-      <c r="C62" s="100" t="s">
-        <v>52</v>
-      </c>
-      <c r="D62" s="101"/>
-      <c r="E62" s="101"/>
-      <c r="F62" s="101"/>
-      <c r="G62" s="101"/>
-      <c r="H62" s="102"/>
+      <c r="C62" s="56" t="str">
+        <f>E50</f>
+        <v>Yeni Roncancio</v>
+      </c>
+      <c r="D62" s="57"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="G62" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="H62" s="60"/>
       <c r="I62" s="2"/>
       <c r="J62" s="1"/>
       <c r="K62" s="2"/>
@@ -6280,74 +5812,592 @@
       <c r="IU62" s="2"/>
       <c r="IV62" s="2"/>
     </row>
-    <row r="63" spans="1:256" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
+      <c r="C63" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="D63" s="62"/>
+      <c r="E63" s="62"/>
+      <c r="F63" s="62"/>
+      <c r="G63" s="62"/>
+      <c r="H63" s="63"/>
+      <c r="I63" s="2"/>
       <c r="J63" s="1"/>
-    </row>
-    <row r="64" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="2"/>
+      <c r="T63" s="2"/>
+      <c r="U63" s="2"/>
+      <c r="V63" s="2"/>
+      <c r="W63" s="2"/>
+      <c r="X63" s="2"/>
+      <c r="Y63" s="2"/>
+      <c r="Z63" s="2"/>
+      <c r="AA63" s="2"/>
+      <c r="AB63" s="2"/>
+      <c r="AC63" s="2"/>
+      <c r="AD63" s="2"/>
+      <c r="AE63" s="2"/>
+      <c r="AF63" s="2"/>
+      <c r="AG63" s="2"/>
+      <c r="AH63" s="2"/>
+      <c r="AI63" s="2"/>
+      <c r="AJ63" s="2"/>
+      <c r="AK63" s="2"/>
+      <c r="AL63" s="2"/>
+      <c r="AM63" s="2"/>
+      <c r="AN63" s="2"/>
+      <c r="AO63" s="2"/>
+      <c r="AP63" s="2"/>
+      <c r="AQ63" s="2"/>
+      <c r="AR63" s="2"/>
+      <c r="AS63" s="2"/>
+      <c r="AT63" s="2"/>
+      <c r="AU63" s="2"/>
+      <c r="AV63" s="2"/>
+      <c r="AW63" s="2"/>
+      <c r="AX63" s="2"/>
+      <c r="AY63" s="2"/>
+      <c r="AZ63" s="2"/>
+      <c r="BA63" s="2"/>
+      <c r="BB63" s="2"/>
+      <c r="BC63" s="2"/>
+      <c r="BD63" s="2"/>
+      <c r="BE63" s="2"/>
+      <c r="BF63" s="2"/>
+      <c r="BG63" s="2"/>
+      <c r="BH63" s="2"/>
+      <c r="BI63" s="2"/>
+      <c r="BJ63" s="2"/>
+      <c r="BK63" s="2"/>
+      <c r="BL63" s="2"/>
+      <c r="BM63" s="2"/>
+      <c r="BN63" s="2"/>
+      <c r="BO63" s="2"/>
+      <c r="BP63" s="2"/>
+      <c r="BQ63" s="2"/>
+      <c r="BR63" s="2"/>
+      <c r="BS63" s="2"/>
+      <c r="BT63" s="2"/>
+      <c r="BU63" s="2"/>
+      <c r="BV63" s="2"/>
+      <c r="BW63" s="2"/>
+      <c r="BX63" s="2"/>
+      <c r="BY63" s="2"/>
+      <c r="BZ63" s="2"/>
+      <c r="CA63" s="2"/>
+      <c r="CB63" s="2"/>
+      <c r="CC63" s="2"/>
+      <c r="CD63" s="2"/>
+      <c r="CE63" s="2"/>
+      <c r="CF63" s="2"/>
+      <c r="CG63" s="2"/>
+      <c r="CH63" s="2"/>
+      <c r="CI63" s="2"/>
+      <c r="CJ63" s="2"/>
+      <c r="CK63" s="2"/>
+      <c r="CL63" s="2"/>
+      <c r="CM63" s="2"/>
+      <c r="CN63" s="2"/>
+      <c r="CO63" s="2"/>
+      <c r="CP63" s="2"/>
+      <c r="CQ63" s="2"/>
+      <c r="CR63" s="2"/>
+      <c r="CS63" s="2"/>
+      <c r="CT63" s="2"/>
+      <c r="CU63" s="2"/>
+      <c r="CV63" s="2"/>
+      <c r="CW63" s="2"/>
+      <c r="CX63" s="2"/>
+      <c r="CY63" s="2"/>
+      <c r="CZ63" s="2"/>
+      <c r="DA63" s="2"/>
+      <c r="DB63" s="2"/>
+      <c r="DC63" s="2"/>
+      <c r="DD63" s="2"/>
+      <c r="DE63" s="2"/>
+      <c r="DF63" s="2"/>
+      <c r="DG63" s="2"/>
+      <c r="DH63" s="2"/>
+      <c r="DI63" s="2"/>
+      <c r="DJ63" s="2"/>
+      <c r="DK63" s="2"/>
+      <c r="DL63" s="2"/>
+      <c r="DM63" s="2"/>
+      <c r="DN63" s="2"/>
+      <c r="DO63" s="2"/>
+      <c r="DP63" s="2"/>
+      <c r="DQ63" s="2"/>
+      <c r="DR63" s="2"/>
+      <c r="DS63" s="2"/>
+      <c r="DT63" s="2"/>
+      <c r="DU63" s="2"/>
+      <c r="DV63" s="2"/>
+      <c r="DW63" s="2"/>
+      <c r="DX63" s="2"/>
+      <c r="DY63" s="2"/>
+      <c r="DZ63" s="2"/>
+      <c r="EA63" s="2"/>
+      <c r="EB63" s="2"/>
+      <c r="EC63" s="2"/>
+      <c r="ED63" s="2"/>
+      <c r="EE63" s="2"/>
+      <c r="EF63" s="2"/>
+      <c r="EG63" s="2"/>
+      <c r="EH63" s="2"/>
+      <c r="EI63" s="2"/>
+      <c r="EJ63" s="2"/>
+      <c r="EK63" s="2"/>
+      <c r="EL63" s="2"/>
+      <c r="EM63" s="2"/>
+      <c r="EN63" s="2"/>
+      <c r="EO63" s="2"/>
+      <c r="EP63" s="2"/>
+      <c r="EQ63" s="2"/>
+      <c r="ER63" s="2"/>
+      <c r="ES63" s="2"/>
+      <c r="ET63" s="2"/>
+      <c r="EU63" s="2"/>
+      <c r="EV63" s="2"/>
+      <c r="EW63" s="2"/>
+      <c r="EX63" s="2"/>
+      <c r="EY63" s="2"/>
+      <c r="EZ63" s="2"/>
+      <c r="FA63" s="2"/>
+      <c r="FB63" s="2"/>
+      <c r="FC63" s="2"/>
+      <c r="FD63" s="2"/>
+      <c r="FE63" s="2"/>
+      <c r="FF63" s="2"/>
+      <c r="FG63" s="2"/>
+      <c r="FH63" s="2"/>
+      <c r="FI63" s="2"/>
+      <c r="FJ63" s="2"/>
+      <c r="FK63" s="2"/>
+      <c r="FL63" s="2"/>
+      <c r="FM63" s="2"/>
+      <c r="FN63" s="2"/>
+      <c r="FO63" s="2"/>
+      <c r="FP63" s="2"/>
+      <c r="FQ63" s="2"/>
+      <c r="FR63" s="2"/>
+      <c r="FS63" s="2"/>
+      <c r="FT63" s="2"/>
+      <c r="FU63" s="2"/>
+      <c r="FV63" s="2"/>
+      <c r="FW63" s="2"/>
+      <c r="FX63" s="2"/>
+      <c r="FY63" s="2"/>
+      <c r="FZ63" s="2"/>
+      <c r="GA63" s="2"/>
+      <c r="GB63" s="2"/>
+      <c r="GC63" s="2"/>
+      <c r="GD63" s="2"/>
+      <c r="GE63" s="2"/>
+      <c r="GF63" s="2"/>
+      <c r="GG63" s="2"/>
+      <c r="GH63" s="2"/>
+      <c r="GI63" s="2"/>
+      <c r="GJ63" s="2"/>
+      <c r="GK63" s="2"/>
+      <c r="GL63" s="2"/>
+      <c r="GM63" s="2"/>
+      <c r="GN63" s="2"/>
+      <c r="GO63" s="2"/>
+      <c r="GP63" s="2"/>
+      <c r="GQ63" s="2"/>
+      <c r="GR63" s="2"/>
+      <c r="GS63" s="2"/>
+      <c r="GT63" s="2"/>
+      <c r="GU63" s="2"/>
+      <c r="GV63" s="2"/>
+      <c r="GW63" s="2"/>
+      <c r="GX63" s="2"/>
+      <c r="GY63" s="2"/>
+      <c r="GZ63" s="2"/>
+      <c r="HA63" s="2"/>
+      <c r="HB63" s="2"/>
+      <c r="HC63" s="2"/>
+      <c r="HD63" s="2"/>
+      <c r="HE63" s="2"/>
+      <c r="HF63" s="2"/>
+      <c r="HG63" s="2"/>
+      <c r="HH63" s="2"/>
+      <c r="HI63" s="2"/>
+      <c r="HJ63" s="2"/>
+      <c r="HK63" s="2"/>
+      <c r="HL63" s="2"/>
+      <c r="HM63" s="2"/>
+      <c r="HN63" s="2"/>
+      <c r="HO63" s="2"/>
+      <c r="HP63" s="2"/>
+      <c r="HQ63" s="2"/>
+      <c r="HR63" s="2"/>
+      <c r="HS63" s="2"/>
+      <c r="HT63" s="2"/>
+      <c r="HU63" s="2"/>
+      <c r="HV63" s="2"/>
+      <c r="HW63" s="2"/>
+      <c r="HX63" s="2"/>
+      <c r="HY63" s="2"/>
+      <c r="HZ63" s="2"/>
+      <c r="IA63" s="2"/>
+      <c r="IB63" s="2"/>
+      <c r="IC63" s="2"/>
+      <c r="ID63" s="2"/>
+      <c r="IE63" s="2"/>
+      <c r="IF63" s="2"/>
+      <c r="IG63" s="2"/>
+      <c r="IH63" s="2"/>
+      <c r="II63" s="2"/>
+      <c r="IJ63" s="2"/>
+      <c r="IK63" s="2"/>
+      <c r="IL63" s="2"/>
+      <c r="IM63" s="2"/>
+      <c r="IN63" s="2"/>
+      <c r="IO63" s="2"/>
+      <c r="IP63" s="2"/>
+      <c r="IQ63" s="2"/>
+      <c r="IR63" s="2"/>
+      <c r="IS63" s="2"/>
+      <c r="IT63" s="2"/>
+      <c r="IU63" s="2"/>
+      <c r="IV63" s="2"/>
+    </row>
+    <row r="64" spans="1:256" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
+      <c r="C64" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="D64" s="65"/>
+      <c r="E64" s="65"/>
+      <c r="F64" s="65"/>
+      <c r="G64" s="65"/>
+      <c r="H64" s="66"/>
+      <c r="I64" s="2"/>
       <c r="J64" s="1"/>
-    </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H66" s="103"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="2"/>
+      <c r="T64" s="2"/>
+      <c r="U64" s="2"/>
+      <c r="V64" s="2"/>
+      <c r="W64" s="2"/>
+      <c r="X64" s="2"/>
+      <c r="Y64" s="2"/>
+      <c r="Z64" s="2"/>
+      <c r="AA64" s="2"/>
+      <c r="AB64" s="2"/>
+      <c r="AC64" s="2"/>
+      <c r="AD64" s="2"/>
+      <c r="AE64" s="2"/>
+      <c r="AF64" s="2"/>
+      <c r="AG64" s="2"/>
+      <c r="AH64" s="2"/>
+      <c r="AI64" s="2"/>
+      <c r="AJ64" s="2"/>
+      <c r="AK64" s="2"/>
+      <c r="AL64" s="2"/>
+      <c r="AM64" s="2"/>
+      <c r="AN64" s="2"/>
+      <c r="AO64" s="2"/>
+      <c r="AP64" s="2"/>
+      <c r="AQ64" s="2"/>
+      <c r="AR64" s="2"/>
+      <c r="AS64" s="2"/>
+      <c r="AT64" s="2"/>
+      <c r="AU64" s="2"/>
+      <c r="AV64" s="2"/>
+      <c r="AW64" s="2"/>
+      <c r="AX64" s="2"/>
+      <c r="AY64" s="2"/>
+      <c r="AZ64" s="2"/>
+      <c r="BA64" s="2"/>
+      <c r="BB64" s="2"/>
+      <c r="BC64" s="2"/>
+      <c r="BD64" s="2"/>
+      <c r="BE64" s="2"/>
+      <c r="BF64" s="2"/>
+      <c r="BG64" s="2"/>
+      <c r="BH64" s="2"/>
+      <c r="BI64" s="2"/>
+      <c r="BJ64" s="2"/>
+      <c r="BK64" s="2"/>
+      <c r="BL64" s="2"/>
+      <c r="BM64" s="2"/>
+      <c r="BN64" s="2"/>
+      <c r="BO64" s="2"/>
+      <c r="BP64" s="2"/>
+      <c r="BQ64" s="2"/>
+      <c r="BR64" s="2"/>
+      <c r="BS64" s="2"/>
+      <c r="BT64" s="2"/>
+      <c r="BU64" s="2"/>
+      <c r="BV64" s="2"/>
+      <c r="BW64" s="2"/>
+      <c r="BX64" s="2"/>
+      <c r="BY64" s="2"/>
+      <c r="BZ64" s="2"/>
+      <c r="CA64" s="2"/>
+      <c r="CB64" s="2"/>
+      <c r="CC64" s="2"/>
+      <c r="CD64" s="2"/>
+      <c r="CE64" s="2"/>
+      <c r="CF64" s="2"/>
+      <c r="CG64" s="2"/>
+      <c r="CH64" s="2"/>
+      <c r="CI64" s="2"/>
+      <c r="CJ64" s="2"/>
+      <c r="CK64" s="2"/>
+      <c r="CL64" s="2"/>
+      <c r="CM64" s="2"/>
+      <c r="CN64" s="2"/>
+      <c r="CO64" s="2"/>
+      <c r="CP64" s="2"/>
+      <c r="CQ64" s="2"/>
+      <c r="CR64" s="2"/>
+      <c r="CS64" s="2"/>
+      <c r="CT64" s="2"/>
+      <c r="CU64" s="2"/>
+      <c r="CV64" s="2"/>
+      <c r="CW64" s="2"/>
+      <c r="CX64" s="2"/>
+      <c r="CY64" s="2"/>
+      <c r="CZ64" s="2"/>
+      <c r="DA64" s="2"/>
+      <c r="DB64" s="2"/>
+      <c r="DC64" s="2"/>
+      <c r="DD64" s="2"/>
+      <c r="DE64" s="2"/>
+      <c r="DF64" s="2"/>
+      <c r="DG64" s="2"/>
+      <c r="DH64" s="2"/>
+      <c r="DI64" s="2"/>
+      <c r="DJ64" s="2"/>
+      <c r="DK64" s="2"/>
+      <c r="DL64" s="2"/>
+      <c r="DM64" s="2"/>
+      <c r="DN64" s="2"/>
+      <c r="DO64" s="2"/>
+      <c r="DP64" s="2"/>
+      <c r="DQ64" s="2"/>
+      <c r="DR64" s="2"/>
+      <c r="DS64" s="2"/>
+      <c r="DT64" s="2"/>
+      <c r="DU64" s="2"/>
+      <c r="DV64" s="2"/>
+      <c r="DW64" s="2"/>
+      <c r="DX64" s="2"/>
+      <c r="DY64" s="2"/>
+      <c r="DZ64" s="2"/>
+      <c r="EA64" s="2"/>
+      <c r="EB64" s="2"/>
+      <c r="EC64" s="2"/>
+      <c r="ED64" s="2"/>
+      <c r="EE64" s="2"/>
+      <c r="EF64" s="2"/>
+      <c r="EG64" s="2"/>
+      <c r="EH64" s="2"/>
+      <c r="EI64" s="2"/>
+      <c r="EJ64" s="2"/>
+      <c r="EK64" s="2"/>
+      <c r="EL64" s="2"/>
+      <c r="EM64" s="2"/>
+      <c r="EN64" s="2"/>
+      <c r="EO64" s="2"/>
+      <c r="EP64" s="2"/>
+      <c r="EQ64" s="2"/>
+      <c r="ER64" s="2"/>
+      <c r="ES64" s="2"/>
+      <c r="ET64" s="2"/>
+      <c r="EU64" s="2"/>
+      <c r="EV64" s="2"/>
+      <c r="EW64" s="2"/>
+      <c r="EX64" s="2"/>
+      <c r="EY64" s="2"/>
+      <c r="EZ64" s="2"/>
+      <c r="FA64" s="2"/>
+      <c r="FB64" s="2"/>
+      <c r="FC64" s="2"/>
+      <c r="FD64" s="2"/>
+      <c r="FE64" s="2"/>
+      <c r="FF64" s="2"/>
+      <c r="FG64" s="2"/>
+      <c r="FH64" s="2"/>
+      <c r="FI64" s="2"/>
+      <c r="FJ64" s="2"/>
+      <c r="FK64" s="2"/>
+      <c r="FL64" s="2"/>
+      <c r="FM64" s="2"/>
+      <c r="FN64" s="2"/>
+      <c r="FO64" s="2"/>
+      <c r="FP64" s="2"/>
+      <c r="FQ64" s="2"/>
+      <c r="FR64" s="2"/>
+      <c r="FS64" s="2"/>
+      <c r="FT64" s="2"/>
+      <c r="FU64" s="2"/>
+      <c r="FV64" s="2"/>
+      <c r="FW64" s="2"/>
+      <c r="FX64" s="2"/>
+      <c r="FY64" s="2"/>
+      <c r="FZ64" s="2"/>
+      <c r="GA64" s="2"/>
+      <c r="GB64" s="2"/>
+      <c r="GC64" s="2"/>
+      <c r="GD64" s="2"/>
+      <c r="GE64" s="2"/>
+      <c r="GF64" s="2"/>
+      <c r="GG64" s="2"/>
+      <c r="GH64" s="2"/>
+      <c r="GI64" s="2"/>
+      <c r="GJ64" s="2"/>
+      <c r="GK64" s="2"/>
+      <c r="GL64" s="2"/>
+      <c r="GM64" s="2"/>
+      <c r="GN64" s="2"/>
+      <c r="GO64" s="2"/>
+      <c r="GP64" s="2"/>
+      <c r="GQ64" s="2"/>
+      <c r="GR64" s="2"/>
+      <c r="GS64" s="2"/>
+      <c r="GT64" s="2"/>
+      <c r="GU64" s="2"/>
+      <c r="GV64" s="2"/>
+      <c r="GW64" s="2"/>
+      <c r="GX64" s="2"/>
+      <c r="GY64" s="2"/>
+      <c r="GZ64" s="2"/>
+      <c r="HA64" s="2"/>
+      <c r="HB64" s="2"/>
+      <c r="HC64" s="2"/>
+      <c r="HD64" s="2"/>
+      <c r="HE64" s="2"/>
+      <c r="HF64" s="2"/>
+      <c r="HG64" s="2"/>
+      <c r="HH64" s="2"/>
+      <c r="HI64" s="2"/>
+      <c r="HJ64" s="2"/>
+      <c r="HK64" s="2"/>
+      <c r="HL64" s="2"/>
+      <c r="HM64" s="2"/>
+      <c r="HN64" s="2"/>
+      <c r="HO64" s="2"/>
+      <c r="HP64" s="2"/>
+      <c r="HQ64" s="2"/>
+      <c r="HR64" s="2"/>
+      <c r="HS64" s="2"/>
+      <c r="HT64" s="2"/>
+      <c r="HU64" s="2"/>
+      <c r="HV64" s="2"/>
+      <c r="HW64" s="2"/>
+      <c r="HX64" s="2"/>
+      <c r="HY64" s="2"/>
+      <c r="HZ64" s="2"/>
+      <c r="IA64" s="2"/>
+      <c r="IB64" s="2"/>
+      <c r="IC64" s="2"/>
+      <c r="ID64" s="2"/>
+      <c r="IE64" s="2"/>
+      <c r="IF64" s="2"/>
+      <c r="IG64" s="2"/>
+      <c r="IH64" s="2"/>
+      <c r="II64" s="2"/>
+      <c r="IJ64" s="2"/>
+      <c r="IK64" s="2"/>
+      <c r="IL64" s="2"/>
+      <c r="IM64" s="2"/>
+      <c r="IN64" s="2"/>
+      <c r="IO64" s="2"/>
+      <c r="IP64" s="2"/>
+      <c r="IQ64" s="2"/>
+      <c r="IR64" s="2"/>
+      <c r="IS64" s="2"/>
+      <c r="IT64" s="2"/>
+      <c r="IU64" s="2"/>
+      <c r="IV64" s="2"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="J65" s="1"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H68" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="C57:H57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="C61:H61"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="C50:H50"/>
-    <mergeCell ref="C51:H56"/>
-    <mergeCell ref="C43:F43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="C3:E4"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="C40:F40"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C3:E4"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="C64:H64"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="C52:H52"/>
+    <mergeCell ref="C53:H58"/>
+    <mergeCell ref="C59:H59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="C63:H63"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F33" r:id="rId1" xr:uid="{07865553-6932-4DB8-BF2F-A566B485F792}"/>
+    <hyperlink ref="F35" r:id="rId1" xr:uid="{07865553-6932-4DB8-BF2F-A566B485F792}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>

--- a/backend/app/platforms/logimat/template.xlsx
+++ b/backend/app/platforms/logimat/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\zymo-intranet\backend\app\platforms\logimat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diana.ramirez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E492E1C1-5C35-4AE6-88F0-A2B36162E5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A80D17D-80E3-4C71-9A2A-961729F8CA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-620" windowWidth="19420" windowHeight="11500" xr2:uid="{24C06BA4-7066-42F3-8310-534950C36D3C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{24C06BA4-7066-42F3-8310-534950C36D3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
   <si>
     <t xml:space="preserve">         LOGIMAT S.A.S.</t>
   </si>
@@ -241,14 +241,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,6 +325,12 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -450,7 +456,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -465,6 +471,21 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -586,6 +607,19 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1012,33 +1046,30 @@
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1049,356 +1080,377 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="4" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="21" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="22" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="23" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="24" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="25" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="26" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="27" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="28" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="29" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="2" borderId="19" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="2" borderId="20" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="27" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="3" borderId="19" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="3" borderId="20" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="3" borderId="35" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="13" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="14" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="34" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="33" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="16" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="17" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="18" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="19" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="20" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="35" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="17" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="18" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="33" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="16" fillId="3" borderId="17" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="16" fillId="3" borderId="18" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="16" fillId="3" borderId="33" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="11" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="12" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="13" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="32" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="31" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="14" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="16" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="21" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="22" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="23" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="24" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="25" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="26" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1432,7 +1484,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="0" cy="330989"/>
@@ -1860,21 +1912,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A804AB5-9B7D-4CE4-BE89-EA920ADDC374}">
-  <dimension ref="A1:IV68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:IV66"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="3.28515625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="14.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="47.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" style="2" customWidth="1"/>
-    <col min="9" max="10" width="3.28515625" style="2" customWidth="1"/>
-    <col min="11" max="256" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="257" max="16384" width="10.42578125" style="2" hidden="1"/>
+    <col min="1" max="2" width="3.26953125" style="2" customWidth="1"/>
+    <col min="3" max="4" width="14.54296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.90625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="47.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.54296875" style="2" customWidth="1"/>
+    <col min="9" max="10" width="3.26953125" style="2" customWidth="1"/>
+    <col min="11" max="256" width="0" style="2" hidden="1"/>
+    <col min="257" max="16384" width="10.453125" style="2" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1886,101 +1938,101 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="C3" s="117" t="e" vm="1">
+      <c r="C3" s="118" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="D3" s="118"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="123" t="s">
+      <c r="D3" s="119"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="124"/>
-      <c r="H3" s="125"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="117"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="122"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="123"/>
       <c r="F4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="126" t="s">
+      <c r="G4" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="127"/>
+      <c r="H4" s="114"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
-      <c r="C5" s="128" t="s">
+      <c r="C5" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="129"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="102">
+      <c r="D5" s="111"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="104">
         <v>46126</v>
       </c>
-      <c r="G5" s="103"/>
-      <c r="H5" s="104"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="106"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
-      <c r="C6" s="99" t="s">
+      <c r="C6" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="100"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="102" t="s">
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="103"/>
-      <c r="H6" s="104"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="106"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
-      <c r="C7" s="99" t="s">
+      <c r="C7" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="100"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="102" t="s">
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="103"/>
-      <c r="H7" s="104"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="106"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
-      <c r="C8" s="105" t="s">
+      <c r="C8" s="130" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="106"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="108" t="s">
+      <c r="D8" s="131"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="109"/>
-      <c r="H8" s="110"/>
+      <c r="G8" s="128"/>
+      <c r="H8" s="129"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
-      <c r="C9" s="111" t="s">
+      <c r="C9" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="113"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="126"/>
       <c r="F9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1992,7 +2044,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="C10" s="7" t="s">
         <v>14</v>
@@ -2011,7 +2063,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="11"/>
     </row>
-    <row r="11" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="32" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="C11" s="12">
         <v>1</v>
@@ -2033,947 +2085,1361 @@
       <c r="J11" s="1"/>
       <c r="K11" s="11"/>
     </row>
-    <row r="12" spans="1:11" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="C12" s="12">
-        <v>1</v>
-      </c>
-      <c r="D12" s="13">
-        <v>1</v>
-      </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="15">
-        <v>360001</v>
-      </c>
-      <c r="H12" s="16">
-        <f t="shared" ref="H12:H32" si="0">+G12*D12</f>
-        <v>360001</v>
+        <v>5</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H12" s="21">
+        <f t="shared" ref="H12:H30" si="0">+G12*D12</f>
+        <v>0</v>
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:11" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="C13" s="12">
-        <v>1</v>
-      </c>
-      <c r="D13" s="13">
-        <v>1</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="15">
-        <v>360002</v>
-      </c>
-      <c r="H13" s="16">
+        <v>5</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H13" s="21">
         <f t="shared" si="0"/>
-        <v>360002</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:11" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="C14" s="12">
-        <v>1</v>
-      </c>
-      <c r="D14" s="13">
-        <v>1</v>
-      </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="15">
-        <v>360003</v>
-      </c>
-      <c r="H14" s="16">
+        <v>5</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H14" s="21">
         <f t="shared" si="0"/>
-        <v>360003</v>
+        <v>0</v>
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:11" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="C15" s="12">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13">
-        <v>1</v>
-      </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="15">
-        <v>360004</v>
-      </c>
-      <c r="H15" s="16">
+        <v>5</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H15" s="21">
         <f t="shared" si="0"/>
-        <v>360004</v>
+        <v>0</v>
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:11" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="C16" s="12">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13">
-        <v>1</v>
-      </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="15">
-        <v>360005</v>
-      </c>
-      <c r="H16" s="16">
+        <v>5</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H16" s="21">
         <f t="shared" si="0"/>
-        <v>360005</v>
+        <v>0</v>
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="C17" s="12">
-        <v>1</v>
-      </c>
-      <c r="D17" s="13">
-        <v>1</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="15">
-        <v>360006</v>
-      </c>
-      <c r="H17" s="16">
+        <v>5</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H17" s="21">
         <f t="shared" si="0"/>
-        <v>360006</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="C18" s="12">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13">
-        <v>1</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="15">
-        <v>360007</v>
-      </c>
-      <c r="H18" s="16">
+        <v>5</v>
+      </c>
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H18" s="21">
         <f t="shared" si="0"/>
-        <v>360007</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="C19" s="12">
-        <v>1</v>
-      </c>
-      <c r="D19" s="13">
-        <v>1</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="15">
-        <v>360008</v>
-      </c>
-      <c r="H19" s="16">
+        <v>5</v>
+      </c>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H19" s="21">
         <f t="shared" si="0"/>
-        <v>360008</v>
+        <v>0</v>
       </c>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="C20" s="12">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13">
-        <v>1</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="15">
-        <v>360009</v>
-      </c>
-      <c r="H20" s="16">
+        <v>5</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H20" s="21">
         <f t="shared" si="0"/>
-        <v>360009</v>
+        <v>0</v>
       </c>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="C21" s="12">
-        <v>1</v>
-      </c>
-      <c r="D21" s="13">
-        <v>1</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="15">
-        <v>360010</v>
-      </c>
-      <c r="H21" s="16">
+        <v>5</v>
+      </c>
+      <c r="D21" s="17"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H21" s="21">
         <f t="shared" si="0"/>
-        <v>360010</v>
+        <v>0</v>
       </c>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="C22" s="12">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13">
-        <v>1</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="15">
-        <v>360011</v>
-      </c>
-      <c r="H22" s="16">
+        <v>5</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H22" s="21">
         <f t="shared" si="0"/>
-        <v>360011</v>
+        <v>0</v>
       </c>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="C23" s="12">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13">
-        <v>1</v>
-      </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="15">
-        <v>360012</v>
-      </c>
-      <c r="H23" s="16">
+        <v>5</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H23" s="21">
         <f t="shared" si="0"/>
-        <v>360012</v>
+        <v>0</v>
       </c>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="C24" s="12">
-        <v>1</v>
-      </c>
-      <c r="D24" s="13">
-        <v>1</v>
-      </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="15">
-        <v>360013</v>
-      </c>
-      <c r="H24" s="16">
+        <v>5</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H24" s="21">
         <f t="shared" si="0"/>
-        <v>360013</v>
+        <v>0</v>
       </c>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="C25" s="12">
-        <v>1</v>
-      </c>
-      <c r="D25" s="13">
-        <v>1</v>
-      </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="15">
-        <v>360014</v>
-      </c>
-      <c r="H25" s="16">
+        <v>5</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H25" s="21">
         <f t="shared" si="0"/>
-        <v>360014</v>
+        <v>0</v>
       </c>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="C26" s="12">
-        <v>1</v>
-      </c>
-      <c r="D26" s="13">
-        <v>1</v>
-      </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="15">
-        <v>360015</v>
-      </c>
-      <c r="H26" s="16">
+        <v>5</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H26" s="21">
         <f t="shared" si="0"/>
-        <v>360015</v>
+        <v>0</v>
       </c>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="C27" s="12">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13">
-        <v>1</v>
-      </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="15">
-        <v>360016</v>
-      </c>
-      <c r="H27" s="16">
+        <v>5</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H27" s="21">
         <f t="shared" si="0"/>
-        <v>360016</v>
+        <v>0</v>
       </c>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
       <c r="C28" s="12">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13">
-        <v>1</v>
-      </c>
-      <c r="E28" s="12"/>
-      <c r="F28" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G28" s="15">
-        <v>360017</v>
-      </c>
-      <c r="H28" s="16">
+        <v>5</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H28" s="21">
         <f t="shared" si="0"/>
-        <v>360017</v>
+        <v>0</v>
       </c>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="C29" s="12">
-        <v>1</v>
-      </c>
-      <c r="D29" s="13">
-        <v>1</v>
-      </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="15">
-        <v>360018</v>
-      </c>
-      <c r="H29" s="16">
+        <v>5</v>
+      </c>
+      <c r="D29" s="17"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H29" s="21">
         <f t="shared" si="0"/>
-        <v>360018</v>
+        <v>0</v>
       </c>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:10" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="C30" s="12">
-        <v>1</v>
-      </c>
-      <c r="D30" s="13">
-        <v>1</v>
-      </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G30" s="15">
-        <v>360019</v>
-      </c>
-      <c r="H30" s="16">
-        <f t="shared" si="0"/>
-        <v>360019</v>
-      </c>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="16">
+        <v>5</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="20">
+        <v>160000</v>
+      </c>
+      <c r="H30" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="1"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="25"/>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C32" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="28"/>
       <c r="J32" s="1"/>
     </row>
-    <row r="33" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="C33" s="114"/>
-      <c r="D33" s="115"/>
-      <c r="E33" s="115"/>
-      <c r="F33" s="115"/>
-      <c r="G33" s="115"/>
-      <c r="H33" s="116"/>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:256" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-      <c r="C34" s="88" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="89"/>
-      <c r="H34" s="90"/>
-      <c r="J34" s="1"/>
-    </row>
-    <row r="35" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="C35" s="91" t="s">
+    <row r="33" spans="1:256" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="29"/>
+      <c r="C33" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="92"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="18" t="s">
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="G35" s="19"/>
-      <c r="H35" s="20"/>
-      <c r="J35" s="17"/>
-    </row>
-    <row r="36" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="C36" s="93" t="s">
+      <c r="G33" s="33"/>
+      <c r="H33" s="34"/>
+      <c r="J33" s="29"/>
+    </row>
+    <row r="34" spans="1:256" ht="16" x14ac:dyDescent="0.35">
+      <c r="A34" s="29"/>
+      <c r="C34" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="D36" s="94"/>
-      <c r="E36" s="94"/>
-      <c r="F36" s="94"/>
-      <c r="G36" s="95"/>
-      <c r="H36" s="21">
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="38">
         <f>SUM(H11:H11)</f>
         <v>360000</v>
       </c>
-      <c r="J36" s="17"/>
-    </row>
-    <row r="37" spans="1:256" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="C37" s="93" t="s">
+      <c r="J34" s="29"/>
+    </row>
+    <row r="35" spans="1:256" ht="16" x14ac:dyDescent="0.35">
+      <c r="A35" s="29"/>
+      <c r="C35" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D37" s="94"/>
-      <c r="E37" s="94"/>
-      <c r="F37" s="94"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="21">
-        <f>+H36*19%</f>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="38">
+        <f>+H34*19%</f>
         <v>68400</v>
       </c>
-      <c r="J37" s="17"/>
-    </row>
-    <row r="38" spans="1:256" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="22"/>
-      <c r="C38" s="96" t="s">
+      <c r="J35" s="29"/>
+    </row>
+    <row r="36" spans="1:256" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="39"/>
+      <c r="C36" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="97"/>
-      <c r="E38" s="97"/>
-      <c r="F38" s="97"/>
-      <c r="G38" s="98"/>
-      <c r="H38" s="23">
-        <f>+H36+H37</f>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="43">
+        <f>+H34+H35</f>
         <v>428400</v>
       </c>
-      <c r="I38" s="2"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="2"/>
-      <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="2"/>
-      <c r="W38" s="2"/>
-      <c r="X38" s="2"/>
-      <c r="Y38" s="2"/>
-      <c r="Z38" s="2"/>
-      <c r="AA38" s="2"/>
-      <c r="AB38" s="2"/>
-      <c r="AC38" s="2"/>
-      <c r="AD38" s="2"/>
-      <c r="AE38" s="2"/>
-      <c r="AF38" s="2"/>
-      <c r="AG38" s="2"/>
-      <c r="AH38" s="2"/>
-      <c r="AI38" s="2"/>
-      <c r="AJ38" s="2"/>
-      <c r="AK38" s="2"/>
-      <c r="AL38" s="2"/>
-      <c r="AM38" s="2"/>
-      <c r="AN38" s="2"/>
-      <c r="AO38" s="2"/>
-      <c r="AP38" s="2"/>
-      <c r="AQ38" s="2"/>
-      <c r="AR38" s="2"/>
-      <c r="AS38" s="2"/>
-      <c r="AT38" s="2"/>
-      <c r="AU38" s="2"/>
-      <c r="AV38" s="2"/>
-      <c r="AW38" s="2"/>
-      <c r="AX38" s="2"/>
-      <c r="AY38" s="2"/>
-      <c r="AZ38" s="2"/>
-      <c r="BA38" s="2"/>
-      <c r="BB38" s="2"/>
-      <c r="BC38" s="2"/>
-      <c r="BD38" s="2"/>
-      <c r="BE38" s="2"/>
-      <c r="BF38" s="2"/>
-      <c r="BG38" s="2"/>
-      <c r="BH38" s="2"/>
-      <c r="BI38" s="2"/>
-      <c r="BJ38" s="2"/>
-      <c r="BK38" s="2"/>
-      <c r="BL38" s="2"/>
-      <c r="BM38" s="2"/>
-      <c r="BN38" s="2"/>
-      <c r="BO38" s="2"/>
-      <c r="BP38" s="2"/>
-      <c r="BQ38" s="2"/>
-      <c r="BR38" s="2"/>
-      <c r="BS38" s="2"/>
-      <c r="BT38" s="2"/>
-      <c r="BU38" s="2"/>
-      <c r="BV38" s="2"/>
-      <c r="BW38" s="2"/>
-      <c r="BX38" s="2"/>
-      <c r="BY38" s="2"/>
-      <c r="BZ38" s="2"/>
-      <c r="CA38" s="2"/>
-      <c r="CB38" s="2"/>
-      <c r="CC38" s="2"/>
-      <c r="CD38" s="2"/>
-      <c r="CE38" s="2"/>
-      <c r="CF38" s="2"/>
-      <c r="CG38" s="2"/>
-      <c r="CH38" s="2"/>
-      <c r="CI38" s="2"/>
-      <c r="CJ38" s="2"/>
-      <c r="CK38" s="2"/>
-      <c r="CL38" s="2"/>
-      <c r="CM38" s="2"/>
-      <c r="CN38" s="2"/>
-      <c r="CO38" s="2"/>
-      <c r="CP38" s="2"/>
-      <c r="CQ38" s="2"/>
-      <c r="CR38" s="2"/>
-      <c r="CS38" s="2"/>
-      <c r="CT38" s="2"/>
-      <c r="CU38" s="2"/>
-      <c r="CV38" s="2"/>
-      <c r="CW38" s="2"/>
-      <c r="CX38" s="2"/>
-      <c r="CY38" s="2"/>
-      <c r="CZ38" s="2"/>
-      <c r="DA38" s="2"/>
-      <c r="DB38" s="2"/>
-      <c r="DC38" s="2"/>
-      <c r="DD38" s="2"/>
-      <c r="DE38" s="2"/>
-      <c r="DF38" s="2"/>
-      <c r="DG38" s="2"/>
-      <c r="DH38" s="2"/>
-      <c r="DI38" s="2"/>
-      <c r="DJ38" s="2"/>
-      <c r="DK38" s="2"/>
-      <c r="DL38" s="2"/>
-      <c r="DM38" s="2"/>
-      <c r="DN38" s="2"/>
-      <c r="DO38" s="2"/>
-      <c r="DP38" s="2"/>
-      <c r="DQ38" s="2"/>
-      <c r="DR38" s="2"/>
-      <c r="DS38" s="2"/>
-      <c r="DT38" s="2"/>
-      <c r="DU38" s="2"/>
-      <c r="DV38" s="2"/>
-      <c r="DW38" s="2"/>
-      <c r="DX38" s="2"/>
-      <c r="DY38" s="2"/>
-      <c r="DZ38" s="2"/>
-      <c r="EA38" s="2"/>
-      <c r="EB38" s="2"/>
-      <c r="EC38" s="2"/>
-      <c r="ED38" s="2"/>
-      <c r="EE38" s="2"/>
-      <c r="EF38" s="2"/>
-      <c r="EG38" s="2"/>
-      <c r="EH38" s="2"/>
-      <c r="EI38" s="2"/>
-      <c r="EJ38" s="2"/>
-      <c r="EK38" s="2"/>
-      <c r="EL38" s="2"/>
-      <c r="EM38" s="2"/>
-      <c r="EN38" s="2"/>
-      <c r="EO38" s="2"/>
-      <c r="EP38" s="2"/>
-      <c r="EQ38" s="2"/>
-      <c r="ER38" s="2"/>
-      <c r="ES38" s="2"/>
-      <c r="ET38" s="2"/>
-      <c r="EU38" s="2"/>
-      <c r="EV38" s="2"/>
-      <c r="EW38" s="2"/>
-      <c r="EX38" s="2"/>
-      <c r="EY38" s="2"/>
-      <c r="EZ38" s="2"/>
-      <c r="FA38" s="2"/>
-      <c r="FB38" s="2"/>
-      <c r="FC38" s="2"/>
-      <c r="FD38" s="2"/>
-      <c r="FE38" s="2"/>
-      <c r="FF38" s="2"/>
-      <c r="FG38" s="2"/>
-      <c r="FH38" s="2"/>
-      <c r="FI38" s="2"/>
-      <c r="FJ38" s="2"/>
-      <c r="FK38" s="2"/>
-      <c r="FL38" s="2"/>
-      <c r="FM38" s="2"/>
-      <c r="FN38" s="2"/>
-      <c r="FO38" s="2"/>
-      <c r="FP38" s="2"/>
-      <c r="FQ38" s="2"/>
-      <c r="FR38" s="2"/>
-      <c r="FS38" s="2"/>
-      <c r="FT38" s="2"/>
-      <c r="FU38" s="2"/>
-      <c r="FV38" s="2"/>
-      <c r="FW38" s="2"/>
-      <c r="FX38" s="2"/>
-      <c r="FY38" s="2"/>
-      <c r="FZ38" s="2"/>
-      <c r="GA38" s="2"/>
-      <c r="GB38" s="2"/>
-      <c r="GC38" s="2"/>
-      <c r="GD38" s="2"/>
-      <c r="GE38" s="2"/>
-      <c r="GF38" s="2"/>
-      <c r="GG38" s="2"/>
-      <c r="GH38" s="2"/>
-      <c r="GI38" s="2"/>
-      <c r="GJ38" s="2"/>
-      <c r="GK38" s="2"/>
-      <c r="GL38" s="2"/>
-      <c r="GM38" s="2"/>
-      <c r="GN38" s="2"/>
-      <c r="GO38" s="2"/>
-      <c r="GP38" s="2"/>
-      <c r="GQ38" s="2"/>
-      <c r="GR38" s="2"/>
-      <c r="GS38" s="2"/>
-      <c r="GT38" s="2"/>
-      <c r="GU38" s="2"/>
-      <c r="GV38" s="2"/>
-      <c r="GW38" s="2"/>
-      <c r="GX38" s="2"/>
-      <c r="GY38" s="2"/>
-      <c r="GZ38" s="2"/>
-      <c r="HA38" s="2"/>
-      <c r="HB38" s="2"/>
-      <c r="HC38" s="2"/>
-      <c r="HD38" s="2"/>
-      <c r="HE38" s="2"/>
-      <c r="HF38" s="2"/>
-      <c r="HG38" s="2"/>
-      <c r="HH38" s="2"/>
-      <c r="HI38" s="2"/>
-      <c r="HJ38" s="2"/>
-      <c r="HK38" s="2"/>
-      <c r="HL38" s="2"/>
-      <c r="HM38" s="2"/>
-      <c r="HN38" s="2"/>
-      <c r="HO38" s="2"/>
-      <c r="HP38" s="2"/>
-      <c r="HQ38" s="2"/>
-      <c r="HR38" s="2"/>
-      <c r="HS38" s="2"/>
-      <c r="HT38" s="2"/>
-      <c r="HU38" s="2"/>
-      <c r="HV38" s="2"/>
-      <c r="HW38" s="2"/>
-      <c r="HX38" s="2"/>
-      <c r="HY38" s="2"/>
-      <c r="HZ38" s="2"/>
-      <c r="IA38" s="2"/>
-      <c r="IB38" s="2"/>
-      <c r="IC38" s="2"/>
-      <c r="ID38" s="2"/>
-      <c r="IE38" s="2"/>
-      <c r="IF38" s="2"/>
-      <c r="IG38" s="2"/>
-      <c r="IH38" s="2"/>
-      <c r="II38" s="2"/>
-      <c r="IJ38" s="2"/>
-      <c r="IK38" s="2"/>
-      <c r="IL38" s="2"/>
-      <c r="IM38" s="2"/>
-      <c r="IN38" s="2"/>
-      <c r="IO38" s="2"/>
-      <c r="IP38" s="2"/>
-      <c r="IQ38" s="2"/>
-      <c r="IR38" s="2"/>
-      <c r="IS38" s="2"/>
-      <c r="IT38" s="2"/>
-      <c r="IU38" s="2"/>
-      <c r="IV38" s="2"/>
-    </row>
-    <row r="39" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="C39" s="25" t="s">
+      <c r="I36" s="2"/>
+      <c r="J36" s="39"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+      <c r="Y36" s="2"/>
+      <c r="Z36" s="2"/>
+      <c r="AA36" s="2"/>
+      <c r="AB36" s="2"/>
+      <c r="AC36" s="2"/>
+      <c r="AD36" s="2"/>
+      <c r="AE36" s="2"/>
+      <c r="AF36" s="2"/>
+      <c r="AG36" s="2"/>
+      <c r="AH36" s="2"/>
+      <c r="AI36" s="2"/>
+      <c r="AJ36" s="2"/>
+      <c r="AK36" s="2"/>
+      <c r="AL36" s="2"/>
+      <c r="AM36" s="2"/>
+      <c r="AN36" s="2"/>
+      <c r="AO36" s="2"/>
+      <c r="AP36" s="2"/>
+      <c r="AQ36" s="2"/>
+      <c r="AR36" s="2"/>
+      <c r="AS36" s="2"/>
+      <c r="AT36" s="2"/>
+      <c r="AU36" s="2"/>
+      <c r="AV36" s="2"/>
+      <c r="AW36" s="2"/>
+      <c r="AX36" s="2"/>
+      <c r="AY36" s="2"/>
+      <c r="AZ36" s="2"/>
+      <c r="BA36" s="2"/>
+      <c r="BB36" s="2"/>
+      <c r="BC36" s="2"/>
+      <c r="BD36" s="2"/>
+      <c r="BE36" s="2"/>
+      <c r="BF36" s="2"/>
+      <c r="BG36" s="2"/>
+      <c r="BH36" s="2"/>
+      <c r="BI36" s="2"/>
+      <c r="BJ36" s="2"/>
+      <c r="BK36" s="2"/>
+      <c r="BL36" s="2"/>
+      <c r="BM36" s="2"/>
+      <c r="BN36" s="2"/>
+      <c r="BO36" s="2"/>
+      <c r="BP36" s="2"/>
+      <c r="BQ36" s="2"/>
+      <c r="BR36" s="2"/>
+      <c r="BS36" s="2"/>
+      <c r="BT36" s="2"/>
+      <c r="BU36" s="2"/>
+      <c r="BV36" s="2"/>
+      <c r="BW36" s="2"/>
+      <c r="BX36" s="2"/>
+      <c r="BY36" s="2"/>
+      <c r="BZ36" s="2"/>
+      <c r="CA36" s="2"/>
+      <c r="CB36" s="2"/>
+      <c r="CC36" s="2"/>
+      <c r="CD36" s="2"/>
+      <c r="CE36" s="2"/>
+      <c r="CF36" s="2"/>
+      <c r="CG36" s="2"/>
+      <c r="CH36" s="2"/>
+      <c r="CI36" s="2"/>
+      <c r="CJ36" s="2"/>
+      <c r="CK36" s="2"/>
+      <c r="CL36" s="2"/>
+      <c r="CM36" s="2"/>
+      <c r="CN36" s="2"/>
+      <c r="CO36" s="2"/>
+      <c r="CP36" s="2"/>
+      <c r="CQ36" s="2"/>
+      <c r="CR36" s="2"/>
+      <c r="CS36" s="2"/>
+      <c r="CT36" s="2"/>
+      <c r="CU36" s="2"/>
+      <c r="CV36" s="2"/>
+      <c r="CW36" s="2"/>
+      <c r="CX36" s="2"/>
+      <c r="CY36" s="2"/>
+      <c r="CZ36" s="2"/>
+      <c r="DA36" s="2"/>
+      <c r="DB36" s="2"/>
+      <c r="DC36" s="2"/>
+      <c r="DD36" s="2"/>
+      <c r="DE36" s="2"/>
+      <c r="DF36" s="2"/>
+      <c r="DG36" s="2"/>
+      <c r="DH36" s="2"/>
+      <c r="DI36" s="2"/>
+      <c r="DJ36" s="2"/>
+      <c r="DK36" s="2"/>
+      <c r="DL36" s="2"/>
+      <c r="DM36" s="2"/>
+      <c r="DN36" s="2"/>
+      <c r="DO36" s="2"/>
+      <c r="DP36" s="2"/>
+      <c r="DQ36" s="2"/>
+      <c r="DR36" s="2"/>
+      <c r="DS36" s="2"/>
+      <c r="DT36" s="2"/>
+      <c r="DU36" s="2"/>
+      <c r="DV36" s="2"/>
+      <c r="DW36" s="2"/>
+      <c r="DX36" s="2"/>
+      <c r="DY36" s="2"/>
+      <c r="DZ36" s="2"/>
+      <c r="EA36" s="2"/>
+      <c r="EB36" s="2"/>
+      <c r="EC36" s="2"/>
+      <c r="ED36" s="2"/>
+      <c r="EE36" s="2"/>
+      <c r="EF36" s="2"/>
+      <c r="EG36" s="2"/>
+      <c r="EH36" s="2"/>
+      <c r="EI36" s="2"/>
+      <c r="EJ36" s="2"/>
+      <c r="EK36" s="2"/>
+      <c r="EL36" s="2"/>
+      <c r="EM36" s="2"/>
+      <c r="EN36" s="2"/>
+      <c r="EO36" s="2"/>
+      <c r="EP36" s="2"/>
+      <c r="EQ36" s="2"/>
+      <c r="ER36" s="2"/>
+      <c r="ES36" s="2"/>
+      <c r="ET36" s="2"/>
+      <c r="EU36" s="2"/>
+      <c r="EV36" s="2"/>
+      <c r="EW36" s="2"/>
+      <c r="EX36" s="2"/>
+      <c r="EY36" s="2"/>
+      <c r="EZ36" s="2"/>
+      <c r="FA36" s="2"/>
+      <c r="FB36" s="2"/>
+      <c r="FC36" s="2"/>
+      <c r="FD36" s="2"/>
+      <c r="FE36" s="2"/>
+      <c r="FF36" s="2"/>
+      <c r="FG36" s="2"/>
+      <c r="FH36" s="2"/>
+      <c r="FI36" s="2"/>
+      <c r="FJ36" s="2"/>
+      <c r="FK36" s="2"/>
+      <c r="FL36" s="2"/>
+      <c r="FM36" s="2"/>
+      <c r="FN36" s="2"/>
+      <c r="FO36" s="2"/>
+      <c r="FP36" s="2"/>
+      <c r="FQ36" s="2"/>
+      <c r="FR36" s="2"/>
+      <c r="FS36" s="2"/>
+      <c r="FT36" s="2"/>
+      <c r="FU36" s="2"/>
+      <c r="FV36" s="2"/>
+      <c r="FW36" s="2"/>
+      <c r="FX36" s="2"/>
+      <c r="FY36" s="2"/>
+      <c r="FZ36" s="2"/>
+      <c r="GA36" s="2"/>
+      <c r="GB36" s="2"/>
+      <c r="GC36" s="2"/>
+      <c r="GD36" s="2"/>
+      <c r="GE36" s="2"/>
+      <c r="GF36" s="2"/>
+      <c r="GG36" s="2"/>
+      <c r="GH36" s="2"/>
+      <c r="GI36" s="2"/>
+      <c r="GJ36" s="2"/>
+      <c r="GK36" s="2"/>
+      <c r="GL36" s="2"/>
+      <c r="GM36" s="2"/>
+      <c r="GN36" s="2"/>
+      <c r="GO36" s="2"/>
+      <c r="GP36" s="2"/>
+      <c r="GQ36" s="2"/>
+      <c r="GR36" s="2"/>
+      <c r="GS36" s="2"/>
+      <c r="GT36" s="2"/>
+      <c r="GU36" s="2"/>
+      <c r="GV36" s="2"/>
+      <c r="GW36" s="2"/>
+      <c r="GX36" s="2"/>
+      <c r="GY36" s="2"/>
+      <c r="GZ36" s="2"/>
+      <c r="HA36" s="2"/>
+      <c r="HB36" s="2"/>
+      <c r="HC36" s="2"/>
+      <c r="HD36" s="2"/>
+      <c r="HE36" s="2"/>
+      <c r="HF36" s="2"/>
+      <c r="HG36" s="2"/>
+      <c r="HH36" s="2"/>
+      <c r="HI36" s="2"/>
+      <c r="HJ36" s="2"/>
+      <c r="HK36" s="2"/>
+      <c r="HL36" s="2"/>
+      <c r="HM36" s="2"/>
+      <c r="HN36" s="2"/>
+      <c r="HO36" s="2"/>
+      <c r="HP36" s="2"/>
+      <c r="HQ36" s="2"/>
+      <c r="HR36" s="2"/>
+      <c r="HS36" s="2"/>
+      <c r="HT36" s="2"/>
+      <c r="HU36" s="2"/>
+      <c r="HV36" s="2"/>
+      <c r="HW36" s="2"/>
+      <c r="HX36" s="2"/>
+      <c r="HY36" s="2"/>
+      <c r="HZ36" s="2"/>
+      <c r="IA36" s="2"/>
+      <c r="IB36" s="2"/>
+      <c r="IC36" s="2"/>
+      <c r="ID36" s="2"/>
+      <c r="IE36" s="2"/>
+      <c r="IF36" s="2"/>
+      <c r="IG36" s="2"/>
+      <c r="IH36" s="2"/>
+      <c r="II36" s="2"/>
+      <c r="IJ36" s="2"/>
+      <c r="IK36" s="2"/>
+      <c r="IL36" s="2"/>
+      <c r="IM36" s="2"/>
+      <c r="IN36" s="2"/>
+      <c r="IO36" s="2"/>
+      <c r="IP36" s="2"/>
+      <c r="IQ36" s="2"/>
+      <c r="IR36" s="2"/>
+      <c r="IS36" s="2"/>
+      <c r="IT36" s="2"/>
+      <c r="IU36" s="2"/>
+      <c r="IV36" s="2"/>
+    </row>
+    <row r="37" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="A37" s="44"/>
+      <c r="C37" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="27"/>
-      <c r="J39" s="24"/>
-    </row>
-    <row r="40" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
-      <c r="C40" s="85" t="s">
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="47"/>
+      <c r="J37" s="44"/>
+    </row>
+    <row r="38" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="A38" s="44"/>
+      <c r="C38" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="D40" s="86"/>
-      <c r="E40" s="86"/>
-      <c r="F40" s="87"/>
-      <c r="G40" s="28" t="s">
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="H40" s="29"/>
-      <c r="J40" s="24"/>
-    </row>
-    <row r="41" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="C41" s="67" t="s">
+      <c r="H38" s="52"/>
+      <c r="J38" s="44"/>
+    </row>
+    <row r="39" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="A39" s="44"/>
+      <c r="C39" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="68"/>
-      <c r="E41" s="69" t="s">
+      <c r="D39" s="54"/>
+      <c r="E39" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="F41" s="70"/>
-      <c r="G41" s="30" t="s">
+      <c r="F39" s="134"/>
+      <c r="G39" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="H41" s="29"/>
-      <c r="J41" s="24"/>
-    </row>
-    <row r="42" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A42" s="24"/>
-      <c r="C42" s="67" t="s">
+      <c r="H39" s="52"/>
+      <c r="J39" s="44"/>
+    </row>
+    <row r="40" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="A40" s="44"/>
+      <c r="C40" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="D42" s="68"/>
-      <c r="E42" s="69" t="s">
+      <c r="D40" s="54"/>
+      <c r="E40" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="F42" s="70"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="29"/>
-      <c r="J42" s="24"/>
-    </row>
-    <row r="43" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A43" s="24"/>
-      <c r="C43" s="67" t="s">
+      <c r="F40" s="134"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="52"/>
+      <c r="J40" s="44"/>
+    </row>
+    <row r="41" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="A41" s="44"/>
+      <c r="C41" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="68"/>
-      <c r="E43" s="69" t="s">
+      <c r="D41" s="54"/>
+      <c r="E41" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="F43" s="70"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="29"/>
-      <c r="J43" s="24"/>
-    </row>
-    <row r="44" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A44" s="24"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="29"/>
-      <c r="J44" s="24"/>
-    </row>
-    <row r="45" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="C45" s="85" t="s">
+      <c r="F41" s="134"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="52"/>
+      <c r="J41" s="44"/>
+    </row>
+    <row r="42" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="A42" s="44"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="52"/>
+      <c r="J42" s="44"/>
+    </row>
+    <row r="43" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="A43" s="44"/>
+      <c r="C43" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="D45" s="86"/>
-      <c r="E45" s="86"/>
-      <c r="F45" s="87"/>
-      <c r="G45" s="28" t="s">
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="H45" s="29"/>
-      <c r="J45" s="24"/>
-    </row>
-    <row r="46" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="C46" s="67" t="s">
+      <c r="H43" s="52"/>
+      <c r="J43" s="44"/>
+    </row>
+    <row r="44" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="A44" s="44"/>
+      <c r="C44" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="69" t="s">
+      <c r="D44" s="54"/>
+      <c r="E44" s="133" t="s">
         <v>35</v>
       </c>
-      <c r="F46" s="70"/>
-      <c r="G46" s="30" t="s">
+      <c r="F44" s="134"/>
+      <c r="G44" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="H46" s="29"/>
-      <c r="J46" s="24"/>
-    </row>
-    <row r="47" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A47" s="24"/>
-      <c r="C47" s="67" t="s">
+      <c r="H44" s="52"/>
+      <c r="J44" s="44"/>
+    </row>
+    <row r="45" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="A45" s="44"/>
+      <c r="C45" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D47" s="68"/>
-      <c r="E47" s="69" t="s">
+      <c r="D45" s="54"/>
+      <c r="E45" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="F47" s="70"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="29"/>
-      <c r="J47" s="24"/>
-    </row>
-    <row r="48" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A48" s="24"/>
-      <c r="C48" s="67" t="s">
+      <c r="F45" s="134"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="52"/>
+      <c r="J45" s="44"/>
+    </row>
+    <row r="46" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="A46" s="44"/>
+      <c r="C46" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D48" s="68"/>
-      <c r="E48" s="69" t="s">
+      <c r="D46" s="54"/>
+      <c r="E46" s="133" t="s">
         <v>37</v>
       </c>
-      <c r="F48" s="70"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="29"/>
-      <c r="J48" s="24"/>
-    </row>
-    <row r="49" spans="1:256" x14ac:dyDescent="0.25">
+      <c r="F46" s="134"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="52"/>
+      <c r="J46" s="44"/>
+    </row>
+    <row r="47" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="A47" s="1"/>
+      <c r="C47" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" s="54"/>
+      <c r="E47" s="133" t="s">
+        <v>39</v>
+      </c>
+      <c r="F47" s="134"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="52"/>
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:256" x14ac:dyDescent="0.35">
+      <c r="A48" s="1"/>
+      <c r="C48" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D48" s="54"/>
+      <c r="E48" s="135" t="s">
+        <v>41</v>
+      </c>
+      <c r="F48" s="136"/>
+      <c r="G48" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="H48" s="52"/>
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" spans="1:256" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1"/>
-      <c r="C49" s="67" t="s">
-        <v>38</v>
-      </c>
-      <c r="D49" s="68"/>
-      <c r="E49" s="69" t="s">
-        <v>39</v>
-      </c>
-      <c r="F49" s="70"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="29"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="61"/>
+      <c r="E49" s="62"/>
+      <c r="F49" s="62"/>
+      <c r="G49" s="63"/>
+      <c r="H49" s="64"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="1:256" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
-      <c r="C50" s="67" t="s">
-        <v>40</v>
-      </c>
-      <c r="D50" s="68"/>
-      <c r="E50" s="71" t="s">
-        <v>41</v>
-      </c>
-      <c r="F50" s="72"/>
-      <c r="G50" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="H50" s="29"/>
+      <c r="C50" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="D50" s="66"/>
+      <c r="E50" s="66"/>
+      <c r="F50" s="66"/>
+      <c r="G50" s="66"/>
+      <c r="H50" s="67"/>
+      <c r="I50" s="2"/>
       <c r="J50" s="1"/>
-    </row>
-    <row r="51" spans="1:256" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="2"/>
+      <c r="T50" s="2"/>
+      <c r="U50" s="2"/>
+      <c r="V50" s="2"/>
+      <c r="W50" s="2"/>
+      <c r="X50" s="2"/>
+      <c r="Y50" s="2"/>
+      <c r="Z50" s="2"/>
+      <c r="AA50" s="2"/>
+      <c r="AB50" s="2"/>
+      <c r="AC50" s="2"/>
+      <c r="AD50" s="2"/>
+      <c r="AE50" s="2"/>
+      <c r="AF50" s="2"/>
+      <c r="AG50" s="2"/>
+      <c r="AH50" s="2"/>
+      <c r="AI50" s="2"/>
+      <c r="AJ50" s="2"/>
+      <c r="AK50" s="2"/>
+      <c r="AL50" s="2"/>
+      <c r="AM50" s="2"/>
+      <c r="AN50" s="2"/>
+      <c r="AO50" s="2"/>
+      <c r="AP50" s="2"/>
+      <c r="AQ50" s="2"/>
+      <c r="AR50" s="2"/>
+      <c r="AS50" s="2"/>
+      <c r="AT50" s="2"/>
+      <c r="AU50" s="2"/>
+      <c r="AV50" s="2"/>
+      <c r="AW50" s="2"/>
+      <c r="AX50" s="2"/>
+      <c r="AY50" s="2"/>
+      <c r="AZ50" s="2"/>
+      <c r="BA50" s="2"/>
+      <c r="BB50" s="2"/>
+      <c r="BC50" s="2"/>
+      <c r="BD50" s="2"/>
+      <c r="BE50" s="2"/>
+      <c r="BF50" s="2"/>
+      <c r="BG50" s="2"/>
+      <c r="BH50" s="2"/>
+      <c r="BI50" s="2"/>
+      <c r="BJ50" s="2"/>
+      <c r="BK50" s="2"/>
+      <c r="BL50" s="2"/>
+      <c r="BM50" s="2"/>
+      <c r="BN50" s="2"/>
+      <c r="BO50" s="2"/>
+      <c r="BP50" s="2"/>
+      <c r="BQ50" s="2"/>
+      <c r="BR50" s="2"/>
+      <c r="BS50" s="2"/>
+      <c r="BT50" s="2"/>
+      <c r="BU50" s="2"/>
+      <c r="BV50" s="2"/>
+      <c r="BW50" s="2"/>
+      <c r="BX50" s="2"/>
+      <c r="BY50" s="2"/>
+      <c r="BZ50" s="2"/>
+      <c r="CA50" s="2"/>
+      <c r="CB50" s="2"/>
+      <c r="CC50" s="2"/>
+      <c r="CD50" s="2"/>
+      <c r="CE50" s="2"/>
+      <c r="CF50" s="2"/>
+      <c r="CG50" s="2"/>
+      <c r="CH50" s="2"/>
+      <c r="CI50" s="2"/>
+      <c r="CJ50" s="2"/>
+      <c r="CK50" s="2"/>
+      <c r="CL50" s="2"/>
+      <c r="CM50" s="2"/>
+      <c r="CN50" s="2"/>
+      <c r="CO50" s="2"/>
+      <c r="CP50" s="2"/>
+      <c r="CQ50" s="2"/>
+      <c r="CR50" s="2"/>
+      <c r="CS50" s="2"/>
+      <c r="CT50" s="2"/>
+      <c r="CU50" s="2"/>
+      <c r="CV50" s="2"/>
+      <c r="CW50" s="2"/>
+      <c r="CX50" s="2"/>
+      <c r="CY50" s="2"/>
+      <c r="CZ50" s="2"/>
+      <c r="DA50" s="2"/>
+      <c r="DB50" s="2"/>
+      <c r="DC50" s="2"/>
+      <c r="DD50" s="2"/>
+      <c r="DE50" s="2"/>
+      <c r="DF50" s="2"/>
+      <c r="DG50" s="2"/>
+      <c r="DH50" s="2"/>
+      <c r="DI50" s="2"/>
+      <c r="DJ50" s="2"/>
+      <c r="DK50" s="2"/>
+      <c r="DL50" s="2"/>
+      <c r="DM50" s="2"/>
+      <c r="DN50" s="2"/>
+      <c r="DO50" s="2"/>
+      <c r="DP50" s="2"/>
+      <c r="DQ50" s="2"/>
+      <c r="DR50" s="2"/>
+      <c r="DS50" s="2"/>
+      <c r="DT50" s="2"/>
+      <c r="DU50" s="2"/>
+      <c r="DV50" s="2"/>
+      <c r="DW50" s="2"/>
+      <c r="DX50" s="2"/>
+      <c r="DY50" s="2"/>
+      <c r="DZ50" s="2"/>
+      <c r="EA50" s="2"/>
+      <c r="EB50" s="2"/>
+      <c r="EC50" s="2"/>
+      <c r="ED50" s="2"/>
+      <c r="EE50" s="2"/>
+      <c r="EF50" s="2"/>
+      <c r="EG50" s="2"/>
+      <c r="EH50" s="2"/>
+      <c r="EI50" s="2"/>
+      <c r="EJ50" s="2"/>
+      <c r="EK50" s="2"/>
+      <c r="EL50" s="2"/>
+      <c r="EM50" s="2"/>
+      <c r="EN50" s="2"/>
+      <c r="EO50" s="2"/>
+      <c r="EP50" s="2"/>
+      <c r="EQ50" s="2"/>
+      <c r="ER50" s="2"/>
+      <c r="ES50" s="2"/>
+      <c r="ET50" s="2"/>
+      <c r="EU50" s="2"/>
+      <c r="EV50" s="2"/>
+      <c r="EW50" s="2"/>
+      <c r="EX50" s="2"/>
+      <c r="EY50" s="2"/>
+      <c r="EZ50" s="2"/>
+      <c r="FA50" s="2"/>
+      <c r="FB50" s="2"/>
+      <c r="FC50" s="2"/>
+      <c r="FD50" s="2"/>
+      <c r="FE50" s="2"/>
+      <c r="FF50" s="2"/>
+      <c r="FG50" s="2"/>
+      <c r="FH50" s="2"/>
+      <c r="FI50" s="2"/>
+      <c r="FJ50" s="2"/>
+      <c r="FK50" s="2"/>
+      <c r="FL50" s="2"/>
+      <c r="FM50" s="2"/>
+      <c r="FN50" s="2"/>
+      <c r="FO50" s="2"/>
+      <c r="FP50" s="2"/>
+      <c r="FQ50" s="2"/>
+      <c r="FR50" s="2"/>
+      <c r="FS50" s="2"/>
+      <c r="FT50" s="2"/>
+      <c r="FU50" s="2"/>
+      <c r="FV50" s="2"/>
+      <c r="FW50" s="2"/>
+      <c r="FX50" s="2"/>
+      <c r="FY50" s="2"/>
+      <c r="FZ50" s="2"/>
+      <c r="GA50" s="2"/>
+      <c r="GB50" s="2"/>
+      <c r="GC50" s="2"/>
+      <c r="GD50" s="2"/>
+      <c r="GE50" s="2"/>
+      <c r="GF50" s="2"/>
+      <c r="GG50" s="2"/>
+      <c r="GH50" s="2"/>
+      <c r="GI50" s="2"/>
+      <c r="GJ50" s="2"/>
+      <c r="GK50" s="2"/>
+      <c r="GL50" s="2"/>
+      <c r="GM50" s="2"/>
+      <c r="GN50" s="2"/>
+      <c r="GO50" s="2"/>
+      <c r="GP50" s="2"/>
+      <c r="GQ50" s="2"/>
+      <c r="GR50" s="2"/>
+      <c r="GS50" s="2"/>
+      <c r="GT50" s="2"/>
+      <c r="GU50" s="2"/>
+      <c r="GV50" s="2"/>
+      <c r="GW50" s="2"/>
+      <c r="GX50" s="2"/>
+      <c r="GY50" s="2"/>
+      <c r="GZ50" s="2"/>
+      <c r="HA50" s="2"/>
+      <c r="HB50" s="2"/>
+      <c r="HC50" s="2"/>
+      <c r="HD50" s="2"/>
+      <c r="HE50" s="2"/>
+      <c r="HF50" s="2"/>
+      <c r="HG50" s="2"/>
+      <c r="HH50" s="2"/>
+      <c r="HI50" s="2"/>
+      <c r="HJ50" s="2"/>
+      <c r="HK50" s="2"/>
+      <c r="HL50" s="2"/>
+      <c r="HM50" s="2"/>
+      <c r="HN50" s="2"/>
+      <c r="HO50" s="2"/>
+      <c r="HP50" s="2"/>
+      <c r="HQ50" s="2"/>
+      <c r="HR50" s="2"/>
+      <c r="HS50" s="2"/>
+      <c r="HT50" s="2"/>
+      <c r="HU50" s="2"/>
+      <c r="HV50" s="2"/>
+      <c r="HW50" s="2"/>
+      <c r="HX50" s="2"/>
+      <c r="HY50" s="2"/>
+      <c r="HZ50" s="2"/>
+      <c r="IA50" s="2"/>
+      <c r="IB50" s="2"/>
+      <c r="IC50" s="2"/>
+      <c r="ID50" s="2"/>
+      <c r="IE50" s="2"/>
+      <c r="IF50" s="2"/>
+      <c r="IG50" s="2"/>
+      <c r="IH50" s="2"/>
+      <c r="II50" s="2"/>
+      <c r="IJ50" s="2"/>
+      <c r="IK50" s="2"/>
+      <c r="IL50" s="2"/>
+      <c r="IM50" s="2"/>
+      <c r="IN50" s="2"/>
+      <c r="IO50" s="2"/>
+      <c r="IP50" s="2"/>
+      <c r="IQ50" s="2"/>
+      <c r="IR50" s="2"/>
+      <c r="IS50" s="2"/>
+      <c r="IT50" s="2"/>
+      <c r="IU50" s="2"/>
+      <c r="IV50" s="2"/>
+    </row>
+    <row r="51" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
-      <c r="C51" s="35"/>
-      <c r="D51" s="36"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="39"/>
+      <c r="C51" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="69"/>
+      <c r="H51" s="70"/>
+      <c r="I51" s="2"/>
       <c r="J51" s="1"/>
-    </row>
-    <row r="52" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="2"/>
+      <c r="T51" s="2"/>
+      <c r="U51" s="2"/>
+      <c r="V51" s="2"/>
+      <c r="W51" s="2"/>
+      <c r="X51" s="2"/>
+      <c r="Y51" s="2"/>
+      <c r="Z51" s="2"/>
+      <c r="AA51" s="2"/>
+      <c r="AB51" s="2"/>
+      <c r="AC51" s="2"/>
+      <c r="AD51" s="2"/>
+      <c r="AE51" s="2"/>
+      <c r="AF51" s="2"/>
+      <c r="AG51" s="2"/>
+      <c r="AH51" s="2"/>
+      <c r="AI51" s="2"/>
+      <c r="AJ51" s="2"/>
+      <c r="AK51" s="2"/>
+      <c r="AL51" s="2"/>
+      <c r="AM51" s="2"/>
+      <c r="AN51" s="2"/>
+      <c r="AO51" s="2"/>
+      <c r="AP51" s="2"/>
+      <c r="AQ51" s="2"/>
+      <c r="AR51" s="2"/>
+      <c r="AS51" s="2"/>
+      <c r="AT51" s="2"/>
+      <c r="AU51" s="2"/>
+      <c r="AV51" s="2"/>
+      <c r="AW51" s="2"/>
+      <c r="AX51" s="2"/>
+      <c r="AY51" s="2"/>
+      <c r="AZ51" s="2"/>
+      <c r="BA51" s="2"/>
+      <c r="BB51" s="2"/>
+      <c r="BC51" s="2"/>
+      <c r="BD51" s="2"/>
+      <c r="BE51" s="2"/>
+      <c r="BF51" s="2"/>
+      <c r="BG51" s="2"/>
+      <c r="BH51" s="2"/>
+      <c r="BI51" s="2"/>
+      <c r="BJ51" s="2"/>
+      <c r="BK51" s="2"/>
+      <c r="BL51" s="2"/>
+      <c r="BM51" s="2"/>
+      <c r="BN51" s="2"/>
+      <c r="BO51" s="2"/>
+      <c r="BP51" s="2"/>
+      <c r="BQ51" s="2"/>
+      <c r="BR51" s="2"/>
+      <c r="BS51" s="2"/>
+      <c r="BT51" s="2"/>
+      <c r="BU51" s="2"/>
+      <c r="BV51" s="2"/>
+      <c r="BW51" s="2"/>
+      <c r="BX51" s="2"/>
+      <c r="BY51" s="2"/>
+      <c r="BZ51" s="2"/>
+      <c r="CA51" s="2"/>
+      <c r="CB51" s="2"/>
+      <c r="CC51" s="2"/>
+      <c r="CD51" s="2"/>
+      <c r="CE51" s="2"/>
+      <c r="CF51" s="2"/>
+      <c r="CG51" s="2"/>
+      <c r="CH51" s="2"/>
+      <c r="CI51" s="2"/>
+      <c r="CJ51" s="2"/>
+      <c r="CK51" s="2"/>
+      <c r="CL51" s="2"/>
+      <c r="CM51" s="2"/>
+      <c r="CN51" s="2"/>
+      <c r="CO51" s="2"/>
+      <c r="CP51" s="2"/>
+      <c r="CQ51" s="2"/>
+      <c r="CR51" s="2"/>
+      <c r="CS51" s="2"/>
+      <c r="CT51" s="2"/>
+      <c r="CU51" s="2"/>
+      <c r="CV51" s="2"/>
+      <c r="CW51" s="2"/>
+      <c r="CX51" s="2"/>
+      <c r="CY51" s="2"/>
+      <c r="CZ51" s="2"/>
+      <c r="DA51" s="2"/>
+      <c r="DB51" s="2"/>
+      <c r="DC51" s="2"/>
+      <c r="DD51" s="2"/>
+      <c r="DE51" s="2"/>
+      <c r="DF51" s="2"/>
+      <c r="DG51" s="2"/>
+      <c r="DH51" s="2"/>
+      <c r="DI51" s="2"/>
+      <c r="DJ51" s="2"/>
+      <c r="DK51" s="2"/>
+      <c r="DL51" s="2"/>
+      <c r="DM51" s="2"/>
+      <c r="DN51" s="2"/>
+      <c r="DO51" s="2"/>
+      <c r="DP51" s="2"/>
+      <c r="DQ51" s="2"/>
+      <c r="DR51" s="2"/>
+      <c r="DS51" s="2"/>
+      <c r="DT51" s="2"/>
+      <c r="DU51" s="2"/>
+      <c r="DV51" s="2"/>
+      <c r="DW51" s="2"/>
+      <c r="DX51" s="2"/>
+      <c r="DY51" s="2"/>
+      <c r="DZ51" s="2"/>
+      <c r="EA51" s="2"/>
+      <c r="EB51" s="2"/>
+      <c r="EC51" s="2"/>
+      <c r="ED51" s="2"/>
+      <c r="EE51" s="2"/>
+      <c r="EF51" s="2"/>
+      <c r="EG51" s="2"/>
+      <c r="EH51" s="2"/>
+      <c r="EI51" s="2"/>
+      <c r="EJ51" s="2"/>
+      <c r="EK51" s="2"/>
+      <c r="EL51" s="2"/>
+      <c r="EM51" s="2"/>
+      <c r="EN51" s="2"/>
+      <c r="EO51" s="2"/>
+      <c r="EP51" s="2"/>
+      <c r="EQ51" s="2"/>
+      <c r="ER51" s="2"/>
+      <c r="ES51" s="2"/>
+      <c r="ET51" s="2"/>
+      <c r="EU51" s="2"/>
+      <c r="EV51" s="2"/>
+      <c r="EW51" s="2"/>
+      <c r="EX51" s="2"/>
+      <c r="EY51" s="2"/>
+      <c r="EZ51" s="2"/>
+      <c r="FA51" s="2"/>
+      <c r="FB51" s="2"/>
+      <c r="FC51" s="2"/>
+      <c r="FD51" s="2"/>
+      <c r="FE51" s="2"/>
+      <c r="FF51" s="2"/>
+      <c r="FG51" s="2"/>
+      <c r="FH51" s="2"/>
+      <c r="FI51" s="2"/>
+      <c r="FJ51" s="2"/>
+      <c r="FK51" s="2"/>
+      <c r="FL51" s="2"/>
+      <c r="FM51" s="2"/>
+      <c r="FN51" s="2"/>
+      <c r="FO51" s="2"/>
+      <c r="FP51" s="2"/>
+      <c r="FQ51" s="2"/>
+      <c r="FR51" s="2"/>
+      <c r="FS51" s="2"/>
+      <c r="FT51" s="2"/>
+      <c r="FU51" s="2"/>
+      <c r="FV51" s="2"/>
+      <c r="FW51" s="2"/>
+      <c r="FX51" s="2"/>
+      <c r="FY51" s="2"/>
+      <c r="FZ51" s="2"/>
+      <c r="GA51" s="2"/>
+      <c r="GB51" s="2"/>
+      <c r="GC51" s="2"/>
+      <c r="GD51" s="2"/>
+      <c r="GE51" s="2"/>
+      <c r="GF51" s="2"/>
+      <c r="GG51" s="2"/>
+      <c r="GH51" s="2"/>
+      <c r="GI51" s="2"/>
+      <c r="GJ51" s="2"/>
+      <c r="GK51" s="2"/>
+      <c r="GL51" s="2"/>
+      <c r="GM51" s="2"/>
+      <c r="GN51" s="2"/>
+      <c r="GO51" s="2"/>
+      <c r="GP51" s="2"/>
+      <c r="GQ51" s="2"/>
+      <c r="GR51" s="2"/>
+      <c r="GS51" s="2"/>
+      <c r="GT51" s="2"/>
+      <c r="GU51" s="2"/>
+      <c r="GV51" s="2"/>
+      <c r="GW51" s="2"/>
+      <c r="GX51" s="2"/>
+      <c r="GY51" s="2"/>
+      <c r="GZ51" s="2"/>
+      <c r="HA51" s="2"/>
+      <c r="HB51" s="2"/>
+      <c r="HC51" s="2"/>
+      <c r="HD51" s="2"/>
+      <c r="HE51" s="2"/>
+      <c r="HF51" s="2"/>
+      <c r="HG51" s="2"/>
+      <c r="HH51" s="2"/>
+      <c r="HI51" s="2"/>
+      <c r="HJ51" s="2"/>
+      <c r="HK51" s="2"/>
+      <c r="HL51" s="2"/>
+      <c r="HM51" s="2"/>
+      <c r="HN51" s="2"/>
+      <c r="HO51" s="2"/>
+      <c r="HP51" s="2"/>
+      <c r="HQ51" s="2"/>
+      <c r="HR51" s="2"/>
+      <c r="HS51" s="2"/>
+      <c r="HT51" s="2"/>
+      <c r="HU51" s="2"/>
+      <c r="HV51" s="2"/>
+      <c r="HW51" s="2"/>
+      <c r="HX51" s="2"/>
+      <c r="HY51" s="2"/>
+      <c r="HZ51" s="2"/>
+      <c r="IA51" s="2"/>
+      <c r="IB51" s="2"/>
+      <c r="IC51" s="2"/>
+      <c r="ID51" s="2"/>
+      <c r="IE51" s="2"/>
+      <c r="IF51" s="2"/>
+      <c r="IG51" s="2"/>
+      <c r="IH51" s="2"/>
+      <c r="II51" s="2"/>
+      <c r="IJ51" s="2"/>
+      <c r="IK51" s="2"/>
+      <c r="IL51" s="2"/>
+      <c r="IM51" s="2"/>
+      <c r="IN51" s="2"/>
+      <c r="IO51" s="2"/>
+      <c r="IP51" s="2"/>
+      <c r="IQ51" s="2"/>
+      <c r="IR51" s="2"/>
+      <c r="IS51" s="2"/>
+      <c r="IT51" s="2"/>
+      <c r="IU51" s="2"/>
+      <c r="IV51" s="2"/>
+    </row>
+    <row r="52" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
-      <c r="C52" s="73" t="s">
-        <v>42</v>
-      </c>
-      <c r="D52" s="74"/>
-      <c r="E52" s="74"/>
-      <c r="F52" s="74"/>
-      <c r="G52" s="74"/>
-      <c r="H52" s="75"/>
+      <c r="C52" s="71"/>
+      <c r="D52" s="72"/>
+      <c r="E52" s="72"/>
+      <c r="F52" s="72"/>
+      <c r="G52" s="72"/>
+      <c r="H52" s="73"/>
       <c r="I52" s="2"/>
       <c r="J52" s="1"/>
       <c r="K52" s="2"/>
@@ -3223,16 +3689,14 @@
       <c r="IU52" s="2"/>
       <c r="IV52" s="2"/>
     </row>
-    <row r="53" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
-      <c r="C53" s="76" t="s">
-        <v>43</v>
-      </c>
-      <c r="D53" s="77"/>
-      <c r="E53" s="77"/>
-      <c r="F53" s="77"/>
-      <c r="G53" s="77"/>
-      <c r="H53" s="78"/>
+      <c r="C53" s="71"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="72"/>
+      <c r="F53" s="72"/>
+      <c r="G53" s="72"/>
+      <c r="H53" s="73"/>
       <c r="I53" s="2"/>
       <c r="J53" s="1"/>
       <c r="K53" s="2"/>
@@ -3482,14 +3946,14 @@
       <c r="IU53" s="2"/>
       <c r="IV53" s="2"/>
     </row>
-    <row r="54" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
-      <c r="C54" s="79"/>
-      <c r="D54" s="80"/>
-      <c r="E54" s="80"/>
-      <c r="F54" s="80"/>
-      <c r="G54" s="80"/>
-      <c r="H54" s="81"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="72"/>
+      <c r="F54" s="72"/>
+      <c r="G54" s="72"/>
+      <c r="H54" s="73"/>
       <c r="I54" s="2"/>
       <c r="J54" s="1"/>
       <c r="K54" s="2"/>
@@ -3739,14 +4203,14 @@
       <c r="IU54" s="2"/>
       <c r="IV54" s="2"/>
     </row>
-    <row r="55" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
-      <c r="C55" s="79"/>
-      <c r="D55" s="80"/>
-      <c r="E55" s="80"/>
-      <c r="F55" s="80"/>
-      <c r="G55" s="80"/>
-      <c r="H55" s="81"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="72"/>
+      <c r="E55" s="72"/>
+      <c r="F55" s="72"/>
+      <c r="G55" s="72"/>
+      <c r="H55" s="73"/>
       <c r="I55" s="2"/>
       <c r="J55" s="1"/>
       <c r="K55" s="2"/>
@@ -3996,14 +4460,14 @@
       <c r="IU55" s="2"/>
       <c r="IV55" s="2"/>
     </row>
-    <row r="56" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:256" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="1"/>
-      <c r="C56" s="79"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="80"/>
-      <c r="F56" s="80"/>
-      <c r="G56" s="80"/>
-      <c r="H56" s="81"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="75"/>
+      <c r="E56" s="75"/>
+      <c r="F56" s="75"/>
+      <c r="G56" s="75"/>
+      <c r="H56" s="76"/>
       <c r="I56" s="2"/>
       <c r="J56" s="1"/>
       <c r="K56" s="2"/>
@@ -4253,14 +4717,16 @@
       <c r="IU56" s="2"/>
       <c r="IV56" s="2"/>
     </row>
-    <row r="57" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
-      <c r="C57" s="79"/>
-      <c r="D57" s="80"/>
-      <c r="E57" s="80"/>
-      <c r="F57" s="80"/>
-      <c r="G57" s="80"/>
-      <c r="H57" s="81"/>
+      <c r="C57" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" s="78"/>
+      <c r="E57" s="78"/>
+      <c r="F57" s="78"/>
+      <c r="G57" s="78"/>
+      <c r="H57" s="79"/>
       <c r="I57" s="2"/>
       <c r="J57" s="1"/>
       <c r="K57" s="2"/>
@@ -4510,14 +4976,20 @@
       <c r="IU57" s="2"/>
       <c r="IV57" s="2"/>
     </row>
-    <row r="58" spans="1:256" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
-      <c r="C58" s="82"/>
-      <c r="D58" s="83"/>
-      <c r="E58" s="83"/>
-      <c r="F58" s="83"/>
-      <c r="G58" s="83"/>
-      <c r="H58" s="84"/>
+      <c r="C58" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="D58" s="81"/>
+      <c r="E58" s="82"/>
+      <c r="F58" s="83" t="s">
+        <v>46</v>
+      </c>
+      <c r="G58" s="84" t="s">
+        <v>47</v>
+      </c>
+      <c r="H58" s="85"/>
       <c r="I58" s="2"/>
       <c r="J58" s="1"/>
       <c r="K58" s="2"/>
@@ -4767,16 +5239,16 @@
       <c r="IU58" s="2"/>
       <c r="IV58" s="2"/>
     </row>
-    <row r="59" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:256" customFormat="1" ht="21.5" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
-      <c r="C59" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="51"/>
-      <c r="G59" s="51"/>
-      <c r="H59" s="52"/>
+      <c r="C59" s="86" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59" s="87"/>
+      <c r="E59" s="88"/>
+      <c r="F59" s="89"/>
+      <c r="G59" s="87"/>
+      <c r="H59" s="90"/>
       <c r="I59" s="2"/>
       <c r="J59" s="1"/>
       <c r="K59" s="2"/>
@@ -5026,20 +5498,21 @@
       <c r="IU59" s="2"/>
       <c r="IV59" s="2"/>
     </row>
-    <row r="60" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:256" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="1"/>
-      <c r="C60" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="D60" s="54"/>
-      <c r="E60" s="55"/>
-      <c r="F60" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="G60" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="H60" s="42"/>
+      <c r="C60" s="91" t="str">
+        <f>E48</f>
+        <v>Yeni Roncancio</v>
+      </c>
+      <c r="D60" s="92"/>
+      <c r="E60" s="93"/>
+      <c r="F60" s="94" t="s">
+        <v>49</v>
+      </c>
+      <c r="G60" s="95" t="s">
+        <v>50</v>
+      </c>
+      <c r="H60" s="96"/>
       <c r="I60" s="2"/>
       <c r="J60" s="1"/>
       <c r="K60" s="2"/>
@@ -5289,16 +5762,16 @@
       <c r="IU60" s="2"/>
       <c r="IV60" s="2"/>
     </row>
-    <row r="61" spans="1:256" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:256" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
-      <c r="C61" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="D61" s="44"/>
-      <c r="E61" s="45"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="44"/>
-      <c r="H61" s="47"/>
+      <c r="C61" s="97" t="s">
+        <v>51</v>
+      </c>
+      <c r="D61" s="98"/>
+      <c r="E61" s="98"/>
+      <c r="F61" s="98"/>
+      <c r="G61" s="98"/>
+      <c r="H61" s="99"/>
       <c r="I61" s="2"/>
       <c r="J61" s="1"/>
       <c r="K61" s="2"/>
@@ -5548,21 +6021,16 @@
       <c r="IU61" s="2"/>
       <c r="IV61" s="2"/>
     </row>
-    <row r="62" spans="1:256" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:256" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="1"/>
-      <c r="C62" s="56" t="str">
-        <f>E50</f>
-        <v>Yeni Roncancio</v>
-      </c>
-      <c r="D62" s="57"/>
-      <c r="E62" s="58"/>
-      <c r="F62" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="G62" s="59" t="s">
-        <v>50</v>
-      </c>
-      <c r="H62" s="60"/>
+      <c r="C62" s="100" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" s="101"/>
+      <c r="E62" s="101"/>
+      <c r="F62" s="101"/>
+      <c r="G62" s="101"/>
+      <c r="H62" s="102"/>
       <c r="I62" s="2"/>
       <c r="J62" s="1"/>
       <c r="K62" s="2"/>
@@ -5812,592 +6280,74 @@
       <c r="IU62" s="2"/>
       <c r="IV62" s="2"/>
     </row>
-    <row r="63" spans="1:256" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:256" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
-      <c r="C63" s="61" t="s">
-        <v>51</v>
-      </c>
-      <c r="D63" s="62"/>
-      <c r="E63" s="62"/>
-      <c r="F63" s="62"/>
-      <c r="G63" s="62"/>
-      <c r="H63" s="63"/>
-      <c r="I63" s="2"/>
       <c r="J63" s="1"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" s="2"/>
-      <c r="Q63" s="2"/>
-      <c r="R63" s="2"/>
-      <c r="S63" s="2"/>
-      <c r="T63" s="2"/>
-      <c r="U63" s="2"/>
-      <c r="V63" s="2"/>
-      <c r="W63" s="2"/>
-      <c r="X63" s="2"/>
-      <c r="Y63" s="2"/>
-      <c r="Z63" s="2"/>
-      <c r="AA63" s="2"/>
-      <c r="AB63" s="2"/>
-      <c r="AC63" s="2"/>
-      <c r="AD63" s="2"/>
-      <c r="AE63" s="2"/>
-      <c r="AF63" s="2"/>
-      <c r="AG63" s="2"/>
-      <c r="AH63" s="2"/>
-      <c r="AI63" s="2"/>
-      <c r="AJ63" s="2"/>
-      <c r="AK63" s="2"/>
-      <c r="AL63" s="2"/>
-      <c r="AM63" s="2"/>
-      <c r="AN63" s="2"/>
-      <c r="AO63" s="2"/>
-      <c r="AP63" s="2"/>
-      <c r="AQ63" s="2"/>
-      <c r="AR63" s="2"/>
-      <c r="AS63" s="2"/>
-      <c r="AT63" s="2"/>
-      <c r="AU63" s="2"/>
-      <c r="AV63" s="2"/>
-      <c r="AW63" s="2"/>
-      <c r="AX63" s="2"/>
-      <c r="AY63" s="2"/>
-      <c r="AZ63" s="2"/>
-      <c r="BA63" s="2"/>
-      <c r="BB63" s="2"/>
-      <c r="BC63" s="2"/>
-      <c r="BD63" s="2"/>
-      <c r="BE63" s="2"/>
-      <c r="BF63" s="2"/>
-      <c r="BG63" s="2"/>
-      <c r="BH63" s="2"/>
-      <c r="BI63" s="2"/>
-      <c r="BJ63" s="2"/>
-      <c r="BK63" s="2"/>
-      <c r="BL63" s="2"/>
-      <c r="BM63" s="2"/>
-      <c r="BN63" s="2"/>
-      <c r="BO63" s="2"/>
-      <c r="BP63" s="2"/>
-      <c r="BQ63" s="2"/>
-      <c r="BR63" s="2"/>
-      <c r="BS63" s="2"/>
-      <c r="BT63" s="2"/>
-      <c r="BU63" s="2"/>
-      <c r="BV63" s="2"/>
-      <c r="BW63" s="2"/>
-      <c r="BX63" s="2"/>
-      <c r="BY63" s="2"/>
-      <c r="BZ63" s="2"/>
-      <c r="CA63" s="2"/>
-      <c r="CB63" s="2"/>
-      <c r="CC63" s="2"/>
-      <c r="CD63" s="2"/>
-      <c r="CE63" s="2"/>
-      <c r="CF63" s="2"/>
-      <c r="CG63" s="2"/>
-      <c r="CH63" s="2"/>
-      <c r="CI63" s="2"/>
-      <c r="CJ63" s="2"/>
-      <c r="CK63" s="2"/>
-      <c r="CL63" s="2"/>
-      <c r="CM63" s="2"/>
-      <c r="CN63" s="2"/>
-      <c r="CO63" s="2"/>
-      <c r="CP63" s="2"/>
-      <c r="CQ63" s="2"/>
-      <c r="CR63" s="2"/>
-      <c r="CS63" s="2"/>
-      <c r="CT63" s="2"/>
-      <c r="CU63" s="2"/>
-      <c r="CV63" s="2"/>
-      <c r="CW63" s="2"/>
-      <c r="CX63" s="2"/>
-      <c r="CY63" s="2"/>
-      <c r="CZ63" s="2"/>
-      <c r="DA63" s="2"/>
-      <c r="DB63" s="2"/>
-      <c r="DC63" s="2"/>
-      <c r="DD63" s="2"/>
-      <c r="DE63" s="2"/>
-      <c r="DF63" s="2"/>
-      <c r="DG63" s="2"/>
-      <c r="DH63" s="2"/>
-      <c r="DI63" s="2"/>
-      <c r="DJ63" s="2"/>
-      <c r="DK63" s="2"/>
-      <c r="DL63" s="2"/>
-      <c r="DM63" s="2"/>
-      <c r="DN63" s="2"/>
-      <c r="DO63" s="2"/>
-      <c r="DP63" s="2"/>
-      <c r="DQ63" s="2"/>
-      <c r="DR63" s="2"/>
-      <c r="DS63" s="2"/>
-      <c r="DT63" s="2"/>
-      <c r="DU63" s="2"/>
-      <c r="DV63" s="2"/>
-      <c r="DW63" s="2"/>
-      <c r="DX63" s="2"/>
-      <c r="DY63" s="2"/>
-      <c r="DZ63" s="2"/>
-      <c r="EA63" s="2"/>
-      <c r="EB63" s="2"/>
-      <c r="EC63" s="2"/>
-      <c r="ED63" s="2"/>
-      <c r="EE63" s="2"/>
-      <c r="EF63" s="2"/>
-      <c r="EG63" s="2"/>
-      <c r="EH63" s="2"/>
-      <c r="EI63" s="2"/>
-      <c r="EJ63" s="2"/>
-      <c r="EK63" s="2"/>
-      <c r="EL63" s="2"/>
-      <c r="EM63" s="2"/>
-      <c r="EN63" s="2"/>
-      <c r="EO63" s="2"/>
-      <c r="EP63" s="2"/>
-      <c r="EQ63" s="2"/>
-      <c r="ER63" s="2"/>
-      <c r="ES63" s="2"/>
-      <c r="ET63" s="2"/>
-      <c r="EU63" s="2"/>
-      <c r="EV63" s="2"/>
-      <c r="EW63" s="2"/>
-      <c r="EX63" s="2"/>
-      <c r="EY63" s="2"/>
-      <c r="EZ63" s="2"/>
-      <c r="FA63" s="2"/>
-      <c r="FB63" s="2"/>
-      <c r="FC63" s="2"/>
-      <c r="FD63" s="2"/>
-      <c r="FE63" s="2"/>
-      <c r="FF63" s="2"/>
-      <c r="FG63" s="2"/>
-      <c r="FH63" s="2"/>
-      <c r="FI63" s="2"/>
-      <c r="FJ63" s="2"/>
-      <c r="FK63" s="2"/>
-      <c r="FL63" s="2"/>
-      <c r="FM63" s="2"/>
-      <c r="FN63" s="2"/>
-      <c r="FO63" s="2"/>
-      <c r="FP63" s="2"/>
-      <c r="FQ63" s="2"/>
-      <c r="FR63" s="2"/>
-      <c r="FS63" s="2"/>
-      <c r="FT63" s="2"/>
-      <c r="FU63" s="2"/>
-      <c r="FV63" s="2"/>
-      <c r="FW63" s="2"/>
-      <c r="FX63" s="2"/>
-      <c r="FY63" s="2"/>
-      <c r="FZ63" s="2"/>
-      <c r="GA63" s="2"/>
-      <c r="GB63" s="2"/>
-      <c r="GC63" s="2"/>
-      <c r="GD63" s="2"/>
-      <c r="GE63" s="2"/>
-      <c r="GF63" s="2"/>
-      <c r="GG63" s="2"/>
-      <c r="GH63" s="2"/>
-      <c r="GI63" s="2"/>
-      <c r="GJ63" s="2"/>
-      <c r="GK63" s="2"/>
-      <c r="GL63" s="2"/>
-      <c r="GM63" s="2"/>
-      <c r="GN63" s="2"/>
-      <c r="GO63" s="2"/>
-      <c r="GP63" s="2"/>
-      <c r="GQ63" s="2"/>
-      <c r="GR63" s="2"/>
-      <c r="GS63" s="2"/>
-      <c r="GT63" s="2"/>
-      <c r="GU63" s="2"/>
-      <c r="GV63" s="2"/>
-      <c r="GW63" s="2"/>
-      <c r="GX63" s="2"/>
-      <c r="GY63" s="2"/>
-      <c r="GZ63" s="2"/>
-      <c r="HA63" s="2"/>
-      <c r="HB63" s="2"/>
-      <c r="HC63" s="2"/>
-      <c r="HD63" s="2"/>
-      <c r="HE63" s="2"/>
-      <c r="HF63" s="2"/>
-      <c r="HG63" s="2"/>
-      <c r="HH63" s="2"/>
-      <c r="HI63" s="2"/>
-      <c r="HJ63" s="2"/>
-      <c r="HK63" s="2"/>
-      <c r="HL63" s="2"/>
-      <c r="HM63" s="2"/>
-      <c r="HN63" s="2"/>
-      <c r="HO63" s="2"/>
-      <c r="HP63" s="2"/>
-      <c r="HQ63" s="2"/>
-      <c r="HR63" s="2"/>
-      <c r="HS63" s="2"/>
-      <c r="HT63" s="2"/>
-      <c r="HU63" s="2"/>
-      <c r="HV63" s="2"/>
-      <c r="HW63" s="2"/>
-      <c r="HX63" s="2"/>
-      <c r="HY63" s="2"/>
-      <c r="HZ63" s="2"/>
-      <c r="IA63" s="2"/>
-      <c r="IB63" s="2"/>
-      <c r="IC63" s="2"/>
-      <c r="ID63" s="2"/>
-      <c r="IE63" s="2"/>
-      <c r="IF63" s="2"/>
-      <c r="IG63" s="2"/>
-      <c r="IH63" s="2"/>
-      <c r="II63" s="2"/>
-      <c r="IJ63" s="2"/>
-      <c r="IK63" s="2"/>
-      <c r="IL63" s="2"/>
-      <c r="IM63" s="2"/>
-      <c r="IN63" s="2"/>
-      <c r="IO63" s="2"/>
-      <c r="IP63" s="2"/>
-      <c r="IQ63" s="2"/>
-      <c r="IR63" s="2"/>
-      <c r="IS63" s="2"/>
-      <c r="IT63" s="2"/>
-      <c r="IU63" s="2"/>
-      <c r="IV63" s="2"/>
-    </row>
-    <row r="64" spans="1:256" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:256" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
-      <c r="C64" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="D64" s="65"/>
-      <c r="E64" s="65"/>
-      <c r="F64" s="65"/>
-      <c r="G64" s="65"/>
-      <c r="H64" s="66"/>
-      <c r="I64" s="2"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
       <c r="J64" s="1"/>
-      <c r="K64" s="2"/>
-      <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" s="2"/>
-      <c r="Q64" s="2"/>
-      <c r="R64" s="2"/>
-      <c r="S64" s="2"/>
-      <c r="T64" s="2"/>
-      <c r="U64" s="2"/>
-      <c r="V64" s="2"/>
-      <c r="W64" s="2"/>
-      <c r="X64" s="2"/>
-      <c r="Y64" s="2"/>
-      <c r="Z64" s="2"/>
-      <c r="AA64" s="2"/>
-      <c r="AB64" s="2"/>
-      <c r="AC64" s="2"/>
-      <c r="AD64" s="2"/>
-      <c r="AE64" s="2"/>
-      <c r="AF64" s="2"/>
-      <c r="AG64" s="2"/>
-      <c r="AH64" s="2"/>
-      <c r="AI64" s="2"/>
-      <c r="AJ64" s="2"/>
-      <c r="AK64" s="2"/>
-      <c r="AL64" s="2"/>
-      <c r="AM64" s="2"/>
-      <c r="AN64" s="2"/>
-      <c r="AO64" s="2"/>
-      <c r="AP64" s="2"/>
-      <c r="AQ64" s="2"/>
-      <c r="AR64" s="2"/>
-      <c r="AS64" s="2"/>
-      <c r="AT64" s="2"/>
-      <c r="AU64" s="2"/>
-      <c r="AV64" s="2"/>
-      <c r="AW64" s="2"/>
-      <c r="AX64" s="2"/>
-      <c r="AY64" s="2"/>
-      <c r="AZ64" s="2"/>
-      <c r="BA64" s="2"/>
-      <c r="BB64" s="2"/>
-      <c r="BC64" s="2"/>
-      <c r="BD64" s="2"/>
-      <c r="BE64" s="2"/>
-      <c r="BF64" s="2"/>
-      <c r="BG64" s="2"/>
-      <c r="BH64" s="2"/>
-      <c r="BI64" s="2"/>
-      <c r="BJ64" s="2"/>
-      <c r="BK64" s="2"/>
-      <c r="BL64" s="2"/>
-      <c r="BM64" s="2"/>
-      <c r="BN64" s="2"/>
-      <c r="BO64" s="2"/>
-      <c r="BP64" s="2"/>
-      <c r="BQ64" s="2"/>
-      <c r="BR64" s="2"/>
-      <c r="BS64" s="2"/>
-      <c r="BT64" s="2"/>
-      <c r="BU64" s="2"/>
-      <c r="BV64" s="2"/>
-      <c r="BW64" s="2"/>
-      <c r="BX64" s="2"/>
-      <c r="BY64" s="2"/>
-      <c r="BZ64" s="2"/>
-      <c r="CA64" s="2"/>
-      <c r="CB64" s="2"/>
-      <c r="CC64" s="2"/>
-      <c r="CD64" s="2"/>
-      <c r="CE64" s="2"/>
-      <c r="CF64" s="2"/>
-      <c r="CG64" s="2"/>
-      <c r="CH64" s="2"/>
-      <c r="CI64" s="2"/>
-      <c r="CJ64" s="2"/>
-      <c r="CK64" s="2"/>
-      <c r="CL64" s="2"/>
-      <c r="CM64" s="2"/>
-      <c r="CN64" s="2"/>
-      <c r="CO64" s="2"/>
-      <c r="CP64" s="2"/>
-      <c r="CQ64" s="2"/>
-      <c r="CR64" s="2"/>
-      <c r="CS64" s="2"/>
-      <c r="CT64" s="2"/>
-      <c r="CU64" s="2"/>
-      <c r="CV64" s="2"/>
-      <c r="CW64" s="2"/>
-      <c r="CX64" s="2"/>
-      <c r="CY64" s="2"/>
-      <c r="CZ64" s="2"/>
-      <c r="DA64" s="2"/>
-      <c r="DB64" s="2"/>
-      <c r="DC64" s="2"/>
-      <c r="DD64" s="2"/>
-      <c r="DE64" s="2"/>
-      <c r="DF64" s="2"/>
-      <c r="DG64" s="2"/>
-      <c r="DH64" s="2"/>
-      <c r="DI64" s="2"/>
-      <c r="DJ64" s="2"/>
-      <c r="DK64" s="2"/>
-      <c r="DL64" s="2"/>
-      <c r="DM64" s="2"/>
-      <c r="DN64" s="2"/>
-      <c r="DO64" s="2"/>
-      <c r="DP64" s="2"/>
-      <c r="DQ64" s="2"/>
-      <c r="DR64" s="2"/>
-      <c r="DS64" s="2"/>
-      <c r="DT64" s="2"/>
-      <c r="DU64" s="2"/>
-      <c r="DV64" s="2"/>
-      <c r="DW64" s="2"/>
-      <c r="DX64" s="2"/>
-      <c r="DY64" s="2"/>
-      <c r="DZ64" s="2"/>
-      <c r="EA64" s="2"/>
-      <c r="EB64" s="2"/>
-      <c r="EC64" s="2"/>
-      <c r="ED64" s="2"/>
-      <c r="EE64" s="2"/>
-      <c r="EF64" s="2"/>
-      <c r="EG64" s="2"/>
-      <c r="EH64" s="2"/>
-      <c r="EI64" s="2"/>
-      <c r="EJ64" s="2"/>
-      <c r="EK64" s="2"/>
-      <c r="EL64" s="2"/>
-      <c r="EM64" s="2"/>
-      <c r="EN64" s="2"/>
-      <c r="EO64" s="2"/>
-      <c r="EP64" s="2"/>
-      <c r="EQ64" s="2"/>
-      <c r="ER64" s="2"/>
-      <c r="ES64" s="2"/>
-      <c r="ET64" s="2"/>
-      <c r="EU64" s="2"/>
-      <c r="EV64" s="2"/>
-      <c r="EW64" s="2"/>
-      <c r="EX64" s="2"/>
-      <c r="EY64" s="2"/>
-      <c r="EZ64" s="2"/>
-      <c r="FA64" s="2"/>
-      <c r="FB64" s="2"/>
-      <c r="FC64" s="2"/>
-      <c r="FD64" s="2"/>
-      <c r="FE64" s="2"/>
-      <c r="FF64" s="2"/>
-      <c r="FG64" s="2"/>
-      <c r="FH64" s="2"/>
-      <c r="FI64" s="2"/>
-      <c r="FJ64" s="2"/>
-      <c r="FK64" s="2"/>
-      <c r="FL64" s="2"/>
-      <c r="FM64" s="2"/>
-      <c r="FN64" s="2"/>
-      <c r="FO64" s="2"/>
-      <c r="FP64" s="2"/>
-      <c r="FQ64" s="2"/>
-      <c r="FR64" s="2"/>
-      <c r="FS64" s="2"/>
-      <c r="FT64" s="2"/>
-      <c r="FU64" s="2"/>
-      <c r="FV64" s="2"/>
-      <c r="FW64" s="2"/>
-      <c r="FX64" s="2"/>
-      <c r="FY64" s="2"/>
-      <c r="FZ64" s="2"/>
-      <c r="GA64" s="2"/>
-      <c r="GB64" s="2"/>
-      <c r="GC64" s="2"/>
-      <c r="GD64" s="2"/>
-      <c r="GE64" s="2"/>
-      <c r="GF64" s="2"/>
-      <c r="GG64" s="2"/>
-      <c r="GH64" s="2"/>
-      <c r="GI64" s="2"/>
-      <c r="GJ64" s="2"/>
-      <c r="GK64" s="2"/>
-      <c r="GL64" s="2"/>
-      <c r="GM64" s="2"/>
-      <c r="GN64" s="2"/>
-      <c r="GO64" s="2"/>
-      <c r="GP64" s="2"/>
-      <c r="GQ64" s="2"/>
-      <c r="GR64" s="2"/>
-      <c r="GS64" s="2"/>
-      <c r="GT64" s="2"/>
-      <c r="GU64" s="2"/>
-      <c r="GV64" s="2"/>
-      <c r="GW64" s="2"/>
-      <c r="GX64" s="2"/>
-      <c r="GY64" s="2"/>
-      <c r="GZ64" s="2"/>
-      <c r="HA64" s="2"/>
-      <c r="HB64" s="2"/>
-      <c r="HC64" s="2"/>
-      <c r="HD64" s="2"/>
-      <c r="HE64" s="2"/>
-      <c r="HF64" s="2"/>
-      <c r="HG64" s="2"/>
-      <c r="HH64" s="2"/>
-      <c r="HI64" s="2"/>
-      <c r="HJ64" s="2"/>
-      <c r="HK64" s="2"/>
-      <c r="HL64" s="2"/>
-      <c r="HM64" s="2"/>
-      <c r="HN64" s="2"/>
-      <c r="HO64" s="2"/>
-      <c r="HP64" s="2"/>
-      <c r="HQ64" s="2"/>
-      <c r="HR64" s="2"/>
-      <c r="HS64" s="2"/>
-      <c r="HT64" s="2"/>
-      <c r="HU64" s="2"/>
-      <c r="HV64" s="2"/>
-      <c r="HW64" s="2"/>
-      <c r="HX64" s="2"/>
-      <c r="HY64" s="2"/>
-      <c r="HZ64" s="2"/>
-      <c r="IA64" s="2"/>
-      <c r="IB64" s="2"/>
-      <c r="IC64" s="2"/>
-      <c r="ID64" s="2"/>
-      <c r="IE64" s="2"/>
-      <c r="IF64" s="2"/>
-      <c r="IG64" s="2"/>
-      <c r="IH64" s="2"/>
-      <c r="II64" s="2"/>
-      <c r="IJ64" s="2"/>
-      <c r="IK64" s="2"/>
-      <c r="IL64" s="2"/>
-      <c r="IM64" s="2"/>
-      <c r="IN64" s="2"/>
-      <c r="IO64" s="2"/>
-      <c r="IP64" s="2"/>
-      <c r="IQ64" s="2"/>
-      <c r="IR64" s="2"/>
-      <c r="IS64" s="2"/>
-      <c r="IT64" s="2"/>
-      <c r="IU64" s="2"/>
-      <c r="IV64" s="2"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="J65" s="1"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H68" s="49"/>
+    </row>
+    <row r="66" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H66" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="C57:H57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="C61:H61"/>
+    <mergeCell ref="C62:H62"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="C51:H56"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C31:H31"/>
     <mergeCell ref="C3:E4"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="F5:H5"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="C64:H64"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="C52:H52"/>
-    <mergeCell ref="C53:H58"/>
-    <mergeCell ref="C59:H59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="C63:H63"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="F6:H6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F35" r:id="rId1" xr:uid="{07865553-6932-4DB8-BF2F-A566B485F792}"/>
+    <hyperlink ref="F33" r:id="rId1" xr:uid="{07865553-6932-4DB8-BF2F-A566B485F792}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
